--- a/CBT_2023_1회/산업안전기사_2023_1회_문항등록.xlsx
+++ b/CBT_2023_1회/산업안전기사_2023_1회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="AI7" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험예지훈련 4라운드&lt;/strong&gt;&lt;br&gt;흐름은 &lt;strong&gt;보고 → 캐고 → 세우고 → 다짐한다&lt;/strong&gt;다. &lt;strong&gt;3R 에서 대책을 세우고 4R 에서 그 가운데 하나를 「우리의 행동목표」로 정한다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;현상파악 · 본질추구 · 대책수립 · 행동목표&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험예지훈련 4라운드&lt;/strong&gt;&lt;br&gt;흐름은 &lt;strong&gt;보고 → 캐고 → 세우고 → 다짐한다&lt;/strong&gt;다. &lt;strong&gt;3R에서 대책을 세우고 4R에서 그 가운데 하나를 「우리의 행동목표」로 정한다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;현상파악 · 본질추구 · 대책수립 · 행동목표&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AI13" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산업안전보건법 제5조 — 사업주 등의 의무&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「방침을 세운다」는 것은 조직의 방향을 정하는 일&lt;/strong&gt;이라 &lt;strong&gt;최고 결정권자인 사업주&lt;/strong&gt;의 몫이다. &lt;strong&gt;안전관리자와 관리감독자는 그 방침을 실행하고 보좌&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;기본 방침은 사업주&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95/%EC%A0%9C5%EC%A1%B0" target="_blank"&gt;제5조(사업주 등의 의무)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건법 · 시행 2026. 8. 1.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주(제77조에 따른 특수형태근로종사자로부터 노무를 제공받는 자와 제78조에 따른 물건의 수거ㆍ배달 등을 중개하는 자를 포함한다. 이하 이 조 및 제6조에서 같다)는 다음 각 호의 사항을 이행함으로써 근로자(제77조에 따른 특수형태근로종사자와 제78조에 따른 물건의 수거ㆍ배달 등을 하는 사람을 포함한다. 이하 이 조 및 제6조에서 같다)의 안전 및 건강을 유지ㆍ증진시키고 국가의 산업재해 예방정책을 따라야 한다. &amp;lt;개정 2020.5.26&amp;gt;&lt;br&gt; 1. 이 법과 이 법에 따른 명령으로 정하는 산업재해 예방을 위한 기준&lt;br&gt; 2. 근로자의 신체적 피로와 정신적 스트레스 등을 줄일 수 있는 쾌적한 작업환경의 조성 및 근로조건 개선&lt;br&gt; 3. 해당 사업장의 안전 및 보건에 관한 정보를 근로자에게 제공&lt;br&gt;▶ ② 다음 각 호의 어느 하나에 해당하는 자는 발주ㆍ설계ㆍ제조ㆍ수입 또는 건설을 할 때 이 법과 이 법에 따른 명령으로 정하는 기준을 지켜야 하고, 발주ㆍ설계ㆍ제조ㆍ수입 또는 건설에 사용되는 물건으로 인하여 발생하는 산업재해를 방지하기 위하여 필요한 조치를 하여야 한다.&lt;br&gt; 1. 기계ㆍ기구와 그 밖의 설비를 설계ㆍ제조 또는 수입하는 자&lt;br&gt; 2. 원재료 등을 제조ㆍ수입하는 자&lt;br&gt; 3. 건설물을 발주ㆍ설계ㆍ건설하는 자&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;산업안전보건법 제5조 — 사업주 등의 의무&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「방침을 세운다」는 것은 조직의 방향을 정하는 일&lt;/strong&gt;이라 &lt;strong&gt;최고 결정권자인 사업주&lt;/strong&gt;의 몫이다. &lt;strong&gt;안전관리자와 관리감독자는 그 방침을 실행하고 보좌&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;기본 방침은 사업주&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95/%EC%A0%9C5%EC%A1%B0" target="_blank"&gt;제5조(사업주 등의 의무)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건법 · 시행 2026. 8. 1.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주(제77조에 따른 특수형태근로종사자로부터 노무를 제공받는 자와 제78조에 따른 물건의 수거ㆍ배달 등을 중개하는 자를 포함한다. 이하 이 조 및 제6조에서 같다)는 다음 각 호의 사항을 이행함으로써 근로자(제77조에 따른 특수형태근로종사자와 제78조에 따른 물건의 수거ㆍ배달 등을 하는 사람을 포함한다. 이하 이 조 및 제6조에서 같다)의 안전 및 건강을 유지ㆍ증진시키고 국가의 산업재해 예방정책을 따라야 한다. &amp;lt;개정 2020.5.26&amp;gt;&lt;br&gt; 1. 이 법과 이 법에 따른 명령으로 정하는 산업재해 예방을 위한 기준&lt;br&gt; 2. 근로자의 신체적 피로와 정신적 스트레스 등을 줄일 수 있는 쾌적한 작업환경의 조성 및 근로조건 개선&lt;br&gt; 3. 해당 사업장의 안전 및 보건에 관한 정보를 근로자에게 제공&lt;br&gt;▶ ② 다음 각 호의 어느 하나에 해당하는 자는 발주ㆍ설계ㆍ제조ㆍ수입 또는 건설을 할 때 이 법과 이 법에 따른 명령으로 정하는 기준을 지켜야 하고, 발주ㆍ설계ㆍ제조ㆍ수입 또는 건설에 사용되는 물건으로 인하여 발생하는 산업재해를 방지하기 위하여 필요한 조치를 하여야 한다.&lt;br&gt; 1. 기계ㆍ기구와 그 밖의 설비를 설계ㆍ제조 또는 수입하는 자&lt;br&gt; 2. 원재료 등을 제조ㆍ수입하는 자&lt;br&gt; 3. 건설물을 발주ㆍ설계ㆍ건설하는 자&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="AG22" s="32" t="inlineStr">
         <is>
-          <t>버드의 비율은 &lt;strong&gt;1 : 10 : 30 : 600&lt;/strong&gt;이다. 경상 10 이 15 이면 &lt;strong&gt;1.5배&lt;/strong&gt;이므로 무상해·무사고는 $600 \times 1.5 = 900$ 건이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;하인리히와 버드의 재해구성비율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;하인리히&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;버드&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;비율&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 29 : 300&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 10 : 30 : 600&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;뜻&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중상 1 · 경상 29 · 무상해 300&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중상 1 · 경상 10 · 물적 손해 30 · 무상해·무사고 600&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;합&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;330&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;641&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>버드의 비율은 &lt;strong&gt;1 : 10 : 30 : 600&lt;/strong&gt;이다. 경상 10이 15 이면 &lt;strong&gt;1.5배&lt;/strong&gt;이므로 무상해·무사고는 $600 \times 1.5 = 900$ 건이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;하인리히와 버드의 재해구성비율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;하인리히&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;버드&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;비율&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 29 : 300&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 10 : 30 : 600&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;뜻&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중상 1 · 경상 29 · 무상해 300&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중상 1 · 경상 10 · 물적 손해 30 · 무상해·무사고 600&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;합&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;330&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;641&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH22" s="32" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지식에 기초한 행동&lt;/strong&gt;이다. &lt;strong&gt;처음 겪는 낯선 상황에서 따져 판단하다가 잘못&lt;/strong&gt; 하는 경우다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;라스무센(Rasmussen)의 인간행동 3분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;행동&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;언제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;오류의 성격&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기능(숙련) 기반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;몸에 밴 일을 할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;깜빡함(slip · lapse)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;규칙 기반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아는 규칙을 적용할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;규칙을 잘못 고름&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지식 기반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;처음 겪는 낯선 상황에서 따질 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분석·의사결정의 오류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;지식에 기초한 행동&lt;/strong&gt;이다. &lt;strong&gt;처음 겪는 낯선 상황에서 따져 판단하다가 잘못&lt;/strong&gt;하는 경우다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;라스무센(Rasmussen)의 인간행동 3분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;행동&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;언제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;오류의 성격&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기능(숙련) 기반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;몸에 밴 일을 할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;깜빡함(slip · lapse)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;규칙 기반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아는 규칙을 적용할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;규칙을 잘못 고름&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지식 기반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;처음 겪는 낯선 상황에서 따질 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분석·의사결정의 오류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="U24" s="32" t="inlineStr">
         <is>
-          <t>다음의 FT도에서 정상 사상 T의 발생확률은 얼마인가? (단, X1, X2, X3의 발생확률은 모두 0.1 이다.)</t>
+          <t>다음의 FT도에서 정상 사상 T의 발생확률은 얼마인가? (단, X1, X2, X3의 발생확률은 모두 0.1이다.)</t>
         </is>
       </c>
       <c r="V24" s="32" t="inlineStr"/>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>식으로 적으면 $T = ( X_{1} X_{2} ) ( X_{1} + X_{3} )$ 다. 전개하면 $X_{1} X_{2} X_{1} + X_{1} X_{2} X_{3} = X_{1} X_{2} + X_{1} X_{2} X_{3}$ 인데, &lt;strong&gt;흡수법칙(&lt;/strong&gt;$A + AB = A$&lt;strong&gt;)&lt;/strong&gt;으로 $T = X_{1} X_{2}$ 가 된다. 따라서 $T = 0.1 \times 0.1 = 0.01$ 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;중복사상이 있을 때의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;계산&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그대로 곱한 값&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.01 \times 0.19 = 0.0019$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt; — 흡수법칙을 놓친 값&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;불 대수로 정리한 뒤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X_{1} X_{2} = 0.01$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt; — 맞는 값&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>식으로 적으면 $T = ( X_{1} X_{2} ) ( X_{1} + X_{3} )$다. 전개하면 $X_{1} X_{2} X_{1} + X_{1} X_{2} X_{3} = X_{1} X_{2} + X_{1} X_{2} X_{3}$ 인데, &lt;strong&gt;흡수법칙(&lt;/strong&gt;$A + AB = A$&lt;strong&gt;)&lt;/strong&gt;으로 $T = X_{1} X_{2}$가 된다. 따라서 $T = 0.1 \times 0.1 = 0.01$이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;중복사상이 있을 때의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;계산&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그대로 곱한 값&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.01 \times 0.19 = 0.0019$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt; — 흡수법칙을 놓친 값&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;불 대수로 정리한 뒤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X_{1} X_{2} = 0.01$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt; — 맞는 값&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
         <is>
-          <t>① 0.0019 는 흡수법칙을 적용하지 않고 그대로 곱한 값이다.&lt;br&gt;③ 0.019 는 계산과 맞지 않는다.&lt;br&gt;④ 0.0361 도 맞지 않는다.</t>
+          <t>① 0.0019는 흡수법칙을 적용하지 않고 그대로 곱한 값이다.&lt;br&gt;③ 0.019는 계산과 맞지 않는다.&lt;br&gt;④ 0.0361 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI24" s="32" t="inlineStr">
@@ -4672,17 +4672,17 @@
       </c>
       <c r="AG28" s="32" t="inlineStr">
         <is>
-          <t>$\text{웨버비} = \dfrac{\Delta I}{I}$ 다. &lt;strong&gt;변화를 알아채는 데 필요한 차이(&lt;/strong&gt;$\Delta I$&lt;strong&gt;)를 원래 자극의 크기(&lt;/strong&gt;$I$&lt;strong&gt;)로 나눈&lt;/strong&gt; 값이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감각별 웨버비&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;감각&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;웨버비&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시각(밝기)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 1/60&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 예민하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 1/50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;청각(음의 세기)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 1/10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;후각&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 1/4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;미각(짠맛)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 1/3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 둔하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\text{웨버비} = \dfrac{\Delta I}{I}$다. &lt;strong&gt;변화를 알아채는 데 필요한 차이(&lt;/strong&gt;$\Delta I$&lt;strong&gt;)를 원래 자극의 크기(&lt;/strong&gt;$I$&lt;strong&gt;)로 나눈&lt;/strong&gt; 값이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감각별 웨버비&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;감각&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;웨버비&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시각(밝기)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 1/60&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 예민하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 1/50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;청각(음의 세기)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 1/10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;후각&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 1/4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;미각(짠맛)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 1/3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 둔하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH28" s="32" t="inlineStr">
         <is>
-          <t>② $I / \Delta I$ 는 뒤집힌 식이다.&lt;br&gt;③ $\Delta I \times I$ 라는 식은 없다.&lt;br&gt;④ $( \Delta I - I ) / I$ 도 없다.</t>
+          <t>② $I / \Delta I$는 뒤집힌 식이다.&lt;br&gt;③ $\Delta I \times I$라는 식은 없다.&lt;br&gt;④ $( \Delta I - I ) / I$도 없다.</t>
         </is>
       </c>
       <c r="AI28" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;웨버(Weber)의 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;웨버비가 작을수록 예민&lt;/strong&gt; 하다 — &lt;strong&gt;조금만 달라져도 알아챈다&lt;/strong&gt;는 뜻이다. &lt;strong&gt;원래 자극이 클수록 변화를 알아채려면 더 크게 달라져야&lt;/strong&gt; 한다는 것이 이 법칙의 요지다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\text{웨버비} = \Delta I \div I$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;웨버(Weber)의 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;웨버비가 작을수록 예민&lt;/strong&gt;하다 — &lt;strong&gt;조금만 달라져도 알아챈다&lt;/strong&gt;는 뜻이다. &lt;strong&gt;원래 자극이 클수록 변화를 알아채려면 더 크게 달라져야&lt;/strong&gt; 한다는 것이 이 법칙의 요지다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\text{웨버비} = \Delta I \div I$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4775,11 @@
           <t>옥타브대  Ⅰ         Ⅱ         Ⅲ         Ⅳ&lt;br&gt;log(S/N)  −0.7      0.18      0.6       0.7&lt;br&gt;가중치      1          1          2          1</t>
         </is>
       </c>
-      <c r="W29" s="32" t="inlineStr"/>
+      <c r="W29" s="32" t="inlineStr">
+        <is>
+          <t>safe_A_2023_01_027_stem1.png</t>
+        </is>
+      </c>
       <c r="X29" s="32" t="inlineStr">
         <is>
           <t>0.38</t>
@@ -4805,17 +4809,17 @@
       </c>
       <c r="AG29" s="32" t="inlineStr">
         <is>
-          <t>$AI = \sum ( \log ( S / N ) \times \text{가중치} ) = (-0.7 \times 1 ) + ( 0.18 \times 1 ) + ( 0.6 \times 2 ) + ( 0.7 \times 1 ) =-0.7 + 0.18 + 1.2 + 0.7 = 1.38$ 이다.</t>
+          <t>$AI = \sum ( \log ( S / N ) \times \text{가중치} ) = (-0.7 \times 1 ) + ( 0.18 \times 1 ) + ( 0.6 \times 2 ) + ( 0.7 \times 1 ) =-0.7 + 0.18 + 1.2 + 0.7 = 1.38$이다.</t>
         </is>
       </c>
       <c r="AH29" s="32" t="inlineStr">
         <is>
-          <t>① 0.38 은 계산과 맞지 않는다.&lt;br&gt;② 0.68 도 맞지 않는다.&lt;br&gt;④ 5.68 도 맞지 않는다.</t>
+          <t>① 0.38은 계산과 맞지 않는다.&lt;br&gt;② 0.68 도 맞지 않는다.&lt;br&gt;④ 5.68 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI29" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;명료도 지수(articulation index)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;각 옥타브대의 &lt;/strong&gt;$\log ( S / N )$&lt;strong&gt; 에 가중치를 곱해 모두 더한다&lt;/strong&gt;. &lt;strong&gt;Ⅰ대의 값이 음수(−0.7)&lt;/strong&gt;라 그냥 더하면 값이 줄어드는데, &lt;strong&gt;이 부호를 놓치면 다른 보기로 빠진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\log ( S / N )$&lt;u&gt; × 가중치의 합&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;명료도 지수(articulation index)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;각 옥타브대의 &lt;/strong&gt;$\log ( S / N )$&lt;strong&gt;에 가중치를 곱해 모두 더한다&lt;/strong&gt;. &lt;strong&gt;Ⅰ대의 값이 음수(−0.7)&lt;/strong&gt;라 그냥 더하면 값이 줄어드는데, &lt;strong&gt;이 부호를 놓치면 다른 보기로 빠진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\log ( S / N )$&lt;u&gt; × 가중치의 합&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5072,12 @@
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① 일정 고장률을 달성하는 것은 신뢰도 배분의 문제다.&lt;br&gt;③ 마멸 고장만 발생하게 하는 것은 FMEA 의 목적이 아니다.&lt;br&gt;④ 시험 시간 단축도 FMEA 의 목적이 아니다.</t>
+          <t>① 일정 고장률을 달성하는 것은 신뢰도 배분의 문제다.&lt;br&gt;③ 마멸 고장만 발생하게 하는 것은 FMEA의 목적이 아니다.&lt;br&gt;④ 시험 시간 단축도 FMEA의 목적이 아니다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FMEA(고장형태 및 영향분석)&lt;/strong&gt;&lt;br&gt;FMEA 는 &lt;strong&gt;「이 부품이 이렇게 고장 나면 무슨 일이 벌어지나」&lt;/strong&gt;를 부품마다 따지는 &lt;strong&gt;상향식 · 귀납적 · 정성적&lt;/strong&gt; 기법이다. 그래서 &lt;strong&gt;설계 단계에서 고장을 줄이는 데&lt;/strong&gt; 가장 쓸모 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;고장을 줄이려면 FMEA&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FMEA(고장형태 및 영향분석)&lt;/strong&gt;&lt;br&gt;FMEA는 &lt;strong&gt;「이 부품이 이렇게 고장 나면 무슨 일이 벌어지나」&lt;/strong&gt;를 부품마다 따지는 &lt;strong&gt;상향식 · 귀납적 · 정성적&lt;/strong&gt; 기법이다. 그래서 &lt;strong&gt;설계 단계에서 고장을 줄이는 데&lt;/strong&gt; 가장 쓸모 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;고장을 줄이려면 FMEA&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5196,17 +5200,17 @@
       </c>
       <c r="AG32" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;실제 손실이 예상됨&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA 의 고장 발생확률 β 와 영향&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;β 의 범위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;고장의 영향&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;β = 1.00&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;실제 손실이 발생됨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;반드시 손실&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.10 ≤ β &amp;lt; 1.00&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;실제 손실이 예상됨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0 &amp;lt; β &amp;lt; 0.10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손실 발생의 가능성이 있음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;β = 0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손실의 영향이 없음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;실제 손실이 예상됨&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA의 고장 발생확률 β 와 영향&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;β 의 범위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;고장의 영향&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;β = 1.00&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;실제 손실이 발생됨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;반드시 손실&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.10 ≤ β &amp;lt; 1.00&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;실제 손실이 예상됨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0 &amp;lt; β &amp;lt; 0.10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손실 발생의 가능성이 있음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;β = 0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손실의 영향이 없음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH32" s="32" t="inlineStr">
         <is>
-          <t>① 손실의 영향이 없는 것은 $\beta = 0$ 일 때다.&lt;br&gt;③ 실제 손실이 발생되는 것은 $\beta = 1.00$ 일 때다.&lt;br&gt;④ 손실 발생의 가능성이 있는 것은 $0 &amp;lt; \beta &amp;lt; 0.10$ 일 때다.</t>
+          <t>① 손실의 영향이 없는 것은 $\beta = 0$일 때다.&lt;br&gt;③ 실제 손실이 발생되는 것은 $\beta = 1.00$일 때다.&lt;br&gt;④ 손실 발생의 가능성이 있는 것은 $0 &amp;lt; \beta &amp;lt; 0.10$일 때다.</t>
         </is>
       </c>
       <c r="AI32" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FMEA 의 고장 영향 평가&lt;/strong&gt;&lt;br&gt;네 구간을 &lt;strong&gt;0 · 0~0.1 · 0.1~1 · 1&lt;/strong&gt;로 나누고, &lt;strong&gt;없음 → 가능성 → 예상 → 발생&lt;/strong&gt;으로 짝지어 둔다. &lt;strong&gt;「예상」과 「발생」을 바꿔 놓는 것&lt;/strong&gt;이 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0 없음 · 0~0.1 가능성 · 0.1~1 예상 · 1 발생&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FMEA의 고장 영향 평가&lt;/strong&gt;&lt;br&gt;네 구간을 &lt;strong&gt;0 · 0~0.1 · 0.1~1 · 1&lt;/strong&gt;로 나누고, &lt;strong&gt;없음 → 가능성 → 예상 → 발생&lt;/strong&gt;으로 짝지어 둔다. &lt;strong&gt;「예상」과 「발생」을 바꿔 놓는 것&lt;/strong&gt;이 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0 없음 · 0~0.1 가능성 · 0.1~1 예상 · 1 발생&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5583,17 +5587,17 @@
       </c>
       <c r="AG35" s="32" t="inlineStr">
         <is>
-          <t>분당 배기량은 20 [L/min], 흡기량은 $V_{i} = 20 \times \dfrac{77}{79} \fallingdotseq 19.49$ [L/min] 이다. 산소소비량은 $19.49 \times 0.21 - 20 \times 0.20 \fallingdotseq 0.093$ [L/min] 이고, 에너지소비량은 $0.093 \times 5 \fallingdotseq 0.46$ [kcal/min] 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;산소소비량과 에너지소비량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흡기량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V_{i} = V_{e} \times \dfrac{100 - O_{2} - CO_{2}}{79}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질소량이 같다는 데서 나온다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소소비량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V_{i} \times 0.21 - V_{e} \times O_{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에너지소비량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산소소비량 × 5 [kcal/L]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산소 1 [L] 는 약 5 [kcal]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>분당 배기량은 20 [L/min], 흡기량은 $V_{i} = 20 \times \dfrac{77}{79} \fallingdotseq 19.49$ [L/min]이다. 산소소비량은 $19.49 \times 0.21 - 20 \times 0.20 \fallingdotseq 0.093$ [L/min]이고, 에너지소비량은 $0.093 \times 5 \fallingdotseq 0.46$ [kcal/min]이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;산소소비량과 에너지소비량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흡기량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V_{i} = V_{e} \times \dfrac{100 - O_{2} - CO_{2}}{79}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질소량이 같다는 데서 나온다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소소비량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V_{i} \times 0.21 - V_{e} \times O_{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에너지소비량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산소소비량 × 5 [kcal/L]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산소 1 [L]는 약 5 [kcal]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH35" s="32" t="inlineStr">
         <is>
-          <t>① A 가 0.038 [L/min] 이면 계산과 맞지 않는다.&lt;br&gt;② 0.008 [L/min] 도 맞지 않는다.&lt;br&gt;③ 0.073 [L/min] 도 맞지 않는다.</t>
+          <t>① A가 0.038 [L/min] 이면 계산과 맞지 않는다.&lt;br&gt;② 0.008 [L/min] 도 맞지 않는다.&lt;br&gt;③ 0.073 [L/min] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI35" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산소소비량에 의한 에너지소비량 산출&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;질소는 몸에서 쓰이지 않으므로 들이마신 양과 내쉰 양이 같다&lt;/strong&gt; — 여기서 흡기량 식이 나온다. &lt;strong&gt;산소 1 [L] = 약 5 [kcal]&lt;/strong&gt;라는 환산도 함께 외워 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산소 1 [L] 는 약 5 [kcal]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;산소소비량에 의한 에너지소비량 산출&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;질소는 몸에서 쓰이지 않으므로 들이마신 양과 내쉰 양이 같다&lt;/strong&gt; — 여기서 흡기량 식이 나온다. &lt;strong&gt;산소 1 [L] = 약 5 [kcal]&lt;/strong&gt;라는 환산도 함께 외워 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산소 1 [L]는 약 5 [kcal]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5841,17 +5845,17 @@
       </c>
       <c r="AG37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Other than 은 「완전한 대체」&lt;/strong&gt;다. &lt;strong&gt;「기타 환경적인 요인」&lt;/strong&gt;이라는 뜻이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;HAZOP 의 가이드워드&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가이드워드&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;No/Not&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 의도가 전혀 이루어지지 않음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;흐름이 없다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;More/Less&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적인 증가 또는 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;유량이 많다/적다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;As well as&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성질상의 증가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;의도한 것 말고 다른 것도 함께&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Part of&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성질상의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;일부만 이루어짐&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Reverse&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 의도와 정반대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;역류&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Other than&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;완전한 대체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전혀 다른 것으로 바뀜&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;Other than은 「완전한 대체」&lt;/strong&gt;다. &lt;strong&gt;「기타 환경적인 요인」&lt;/strong&gt;이라는 뜻이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;HAZOP의 가이드워드&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가이드워드&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;No/Not&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 의도가 전혀 이루어지지 않음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;흐름이 없다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;More/Less&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적인 증가 또는 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;유량이 많다/적다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;As well as&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성질상의 증가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;의도한 것 말고 다른 것도 함께&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Part of&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성질상의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;일부만 이루어짐&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Reverse&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 의도와 정반대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;역류&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Other than&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;완전한 대체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전혀 다른 것으로 바뀜&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH37" s="32" t="inlineStr">
         <is>
-          <t>① As well as 가 성질상의 증가인 것은 맞다.&lt;br&gt;② More/Less 가 정량적인 증가·감소인 것도 맞다.&lt;br&gt;③ Part of 가 성질상의 감소인 것도 맞다.</t>
+          <t>① As well as가 성질상의 증가인 것은 맞다.&lt;br&gt;② More/Less가 정량적인 증가·감소인 것도 맞다.&lt;br&gt;③ Part of가 성질상의 감소인 것도 맞다.</t>
         </is>
       </c>
       <c r="AI37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;HAZOP 의 가이드워드&lt;/strong&gt;&lt;br&gt;여섯을 &lt;strong&gt;없다(No) · 많다/적다(More/Less) · 더 있다(As well as) · 일부만(Part of) · 거꾸로(Reverse) · 딴것으로(Other than)&lt;/strong&gt;로 새긴다. &lt;strong&gt;Other than 은 「그 밖의」가 아니라 「전혀 다른 것」&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Other than 은 완전한 대체&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;HAZOP의 가이드워드&lt;/strong&gt;&lt;br&gt;여섯을 &lt;strong&gt;없다(No) · 많다/적다(More/Less) · 더 있다(As well as) · 일부만(Part of) · 거꾸로(Reverse) · 딴것으로(Other than)&lt;/strong&gt;로 새긴다. &lt;strong&gt;Other than은 「그 밖의」가 아니라 「전혀 다른 것」&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Other than은 완전한 대체&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5970,17 +5974,17 @@
       </c>
       <c r="AG38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;PHA(예비위험분석)&lt;/strong&gt;다. &lt;strong&gt;가장 이른 단계에서 정성적으로 훑는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;PHA 의 위험 4등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;카테고리 Ⅰ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파국적(catastrophic)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사망이나 시스템 손실&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;카테고리 Ⅱ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;위기적(critical)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중대한 상해나 시스템 손상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;카테고리 Ⅲ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한계적(marginal)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;경미한 상해 · 대처 가능&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;카테고리 Ⅳ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;무시가능(negligible)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;상해나 손상이 없다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;PHA(예비위험분석)&lt;/strong&gt;다. &lt;strong&gt;가장 이른 단계에서 정성적으로 훑는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;PHA의 위험 4등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;카테고리 Ⅰ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파국적(catastrophic)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사망이나 시스템 손실&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;카테고리 Ⅱ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;위기적(critical)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중대한 상해나 시스템 손상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;카테고리 Ⅲ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한계적(marginal)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;경미한 상해 · 대처 가능&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;카테고리 Ⅳ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;무시가능(negligible)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;상해나 손상이 없다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH38" s="32" t="inlineStr">
         <is>
-          <t>② FHA 는 분담 설계에서 다른 곳의 영향을 보는 기법이다.&lt;br&gt;③ FMEA 는 설계 단계의 귀납적 기법이다.&lt;br&gt;④ FTA 는 정량적·연역적 기법이다.</t>
+          <t>② FHA는 분담 설계에서 다른 곳의 영향을 보는 기법이다.&lt;br&gt;③ FMEA는 설계 단계의 귀납적 기법이다.&lt;br&gt;④ FTA는 정량적·연역적 기법이다.</t>
         </is>
       </c>
       <c r="AI38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;PHA(예비위험분석)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;PHA 의 P 가 Preliminary(예비)&lt;/strong&gt;다. &lt;strong&gt;아직 설계도 없는 구상 단계에서 「무엇이 위험할까」를 먼저 훑는&lt;/strong&gt; 것이라 가장 앞에 온다. &lt;strong&gt;네 등급을 파 · 위 · 한 · 무&lt;/strong&gt;로 새긴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;맨 처음의 정성적 해석은 PHA&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;PHA(예비위험분석)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;PHA의 P가 Preliminary(예비)&lt;/strong&gt;다. &lt;strong&gt;아직 설계도 없는 구상 단계에서 「무엇이 위험할까」를 먼저 훑는&lt;/strong&gt; 것이라 가장 앞에 온다. &lt;strong&gt;네 등급을 파 · 위 · 한 · 무&lt;/strong&gt;로 새긴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;맨 처음의 정성적 해석은 PHA&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6069,7 @@
       </c>
       <c r="U39" s="32" t="inlineStr">
         <is>
-          <t>다음 중 인간의 제어 및 조정능력을 나타내는 법칙인 Fitts' law 와 관련된 변수가 아닌 것은?</t>
+          <t>다음 중 인간의 제어 및 조정능력을 나타내는 법칙인 Fitts' law와 관련된 변수가 아닌 것은?</t>
         </is>
       </c>
       <c r="V39" s="32" t="inlineStr"/>
@@ -6099,7 +6103,7 @@
       </c>
       <c r="AG39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;표적의 색상&lt;/strong&gt;은 식에 들어가지 않는다. $MT = a + b \log_{2} ( \dfrac{2 A}{W} )$ 에는 &lt;strong&gt;거리 &lt;/strong&gt;$A$&lt;strong&gt; 와 너비 &lt;/strong&gt;$W$만 나온다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;Fitts 의 법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;변수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이동 거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;A&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시작점에서 표적까지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;표적의 너비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;W&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;표적의 크기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난이도 지수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ID&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\log_{2} ( 2 A / W )$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이동 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;MT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$a + b \times ID$&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;표적의 색상&lt;/strong&gt;은 식에 들어가지 않는다. $MT = a + b \log_{2} ( \dfrac{2 A}{W} )$에는 &lt;strong&gt;거리 &lt;/strong&gt;$A$&lt;strong&gt;와 너비 &lt;/strong&gt;$W$만 나온다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;Fitts의 법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;변수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이동 거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;A&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시작점에서 표적까지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;표적의 너비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;W&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;표적의 크기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난이도 지수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ID&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\log_{2} ( 2 A / W )$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이동 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;MT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$a + b \times ID$&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH39" s="32" t="inlineStr">
@@ -6109,7 +6113,7 @@
       </c>
       <c r="AI39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Fitts 의 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;거리와 크기, 두 가지뿐&lt;/strong&gt;이다. &lt;strong&gt;색상 · 모양 · 밝기는 「찾는 데」 영향을 주지만 「손을 옮기는 시간」에는 들어가지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;거리와 너비 둘뿐&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;Fitts의 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;거리와 크기, 두 가지뿐&lt;/strong&gt;이다. &lt;strong&gt;색상 · 모양 · 밝기는 「찾는 데」 영향을 주지만 「손을 옮기는 시간」에는 들어가지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;거리와 너비 둘뿐&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6371,7 @@
       </c>
       <c r="AI41" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정성적 표시장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정성적 표시장치도 바탕은 숫자&lt;/strong&gt; 지만, &lt;strong&gt;그 숫자를 「정상 · 주의 · 위험」 같은 구간으로 바꿔 보여 준다&lt;/strong&gt;. &lt;strong&gt;숫자를 그대로 보여 주면 정량적&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;숫자를 그대로 보이면 정량적&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정성적 표시장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정성적 표시장치도 바탕은 숫자&lt;/strong&gt;지만, &lt;strong&gt;그 숫자를 「정상 · 주의 · 위험」 같은 구간으로 바꿔 보여 준다&lt;/strong&gt;. &lt;strong&gt;숫자를 그대로 보여 주면 정량적&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;숫자를 그대로 보이면 정량적&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6490,7 @@
       </c>
       <c r="AG42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;조도(illuminance)&lt;/strong&gt;다. $\text{조도} = \dfrac{\text{광도}}{\text{거리}^{2}}$ 이며 &lt;strong&gt;면이 얼마나 반사하는지와 무관&lt;/strong&gt; 하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;조명 관련 용어&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용어&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;광속&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;lumen [lm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;광원에서 나오는 빛의 총량&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;광도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;candela [cd]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;광원이 어느 방향으로 내는 빛의 세기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;lux [lx]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;면에 도달한 빛의 양&lt;/u&gt; — $\text{광도} / \text{거리}^{2}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;휘도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[cd/㎡]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;면에서 반사되어 눈에 오는 빛&lt;/u&gt; — 반사율에 좌우된다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반사율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{휘도} / \text{조도}$&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;조도(illuminance)&lt;/strong&gt;다. $\text{조도} = \dfrac{\text{광도}}{\text{거리}^{2}}$이며 &lt;strong&gt;면이 얼마나 반사하는지와 무관&lt;/strong&gt;하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;조명 관련 용어&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용어&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;광속&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;lumen [lm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;광원에서 나오는 빛의 총량&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;광도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;candela [cd]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;광원이 어느 방향으로 내는 빛의 세기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;lux [lx]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;면에 도달한 빛의 양&lt;/u&gt; — $\text{광도} / \text{거리}^{2}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;휘도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[cd/㎡]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;면에서 반사되어 눈에 오는 빛&lt;/u&gt; — 반사율에 좌우된다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반사율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{휘도} / \text{조도}$&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH42" s="32" t="inlineStr">
@@ -6744,12 +6748,12 @@
       </c>
       <c r="AG44" s="32" t="inlineStr">
         <is>
-          <t>분할날 두께는 &lt;strong&gt;톱날 두께의 1.1배 이상이면서 치진폭보다는 작아야&lt;/strong&gt; 한다. $2 \times 1.1 = 2.2$ [mm] 이므로 &lt;strong&gt;2.2 ≤ t &amp;lt; 2.5&lt;/strong&gt; [mm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;목재가공용 둥근톱 분할날의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;두께&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 두께의 1.1배 이상, 치진폭 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$1.1 t_{1} \le t &amp;lt; b$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 원주의 1/4 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;톱날과의 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;12 [mm] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물리는 부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱 뒷날의 2/3 이상을 덮을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>분할날 두께는 &lt;strong&gt;톱날 두께의 1.1배 이상이면서 치진폭보다는 작아야&lt;/strong&gt; 한다. $2 \times 1.1 = 2.2$ [mm]이므로 &lt;strong&gt;2.2 ≤ t &amp;lt; 2.5&lt;/strong&gt; [mm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;목재가공용 둥근톱 분할날의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;두께&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 두께의 1.1배 이상, 치진폭 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$1.1 t_{1} \le t &amp;lt; b$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 원주의 1/4 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;톱날과의 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;12 [mm] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물리는 부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱 뒷날의 2/3 이상을 덮을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH44" s="32" t="inlineStr">
         <is>
-          <t>② 2.0 [mm] 는 1.1배(2.2 [mm]) 에 못 미친다.&lt;br&gt;③ 1.5 [mm] 도 그렇다.&lt;br&gt;④ 2.5 [mm] 는 치진폭과 같거나 커서 톱자국에 끼인다.</t>
+          <t>② 2.0 [mm]는 1.1배(2.2 [mm])에 못 미친다.&lt;br&gt;③ 1.5 [mm] 도 그렇다.&lt;br&gt;④ 2.5 [mm]는 치진폭과 같거나 커서 톱자국에 끼인다.</t>
         </is>
       </c>
       <c r="AI44" s="32" t="inlineStr">
@@ -7131,7 +7135,7 @@
       </c>
       <c r="AG47" s="32" t="inlineStr">
         <is>
-          <t>방진구는 &lt;strong&gt;지름의 12배 이상&lt;/strong&gt; 일 때 쓴다. 5배가 아니다.</t>
+          <t>방진구는 &lt;strong&gt;지름의 12배 이상&lt;/strong&gt;일 때 쓴다. 5배가 아니다.</t>
         </is>
       </c>
       <c r="AH47" s="32" t="inlineStr">
@@ -7260,17 +7264,17 @@
       </c>
       <c r="AG48" s="32" t="inlineStr">
         <is>
-          <t>$T_{m} = ( \dfrac{1}{2} + \dfrac{1}{\text{클러치 맞물림 개소 수}} ) \times \dfrac{60 {,} 000}{\text{매분 행정수}} = ( 0.5 + 0.125 ) \times \dfrac{60 {,} 000}{250} = 0.625 \times 240 = 150$ [ms] 다. 안전거리는 $D = 1.6 T_{m} = 1.6 \times 150 = 240$ [mm] 다.</t>
+          <t>$T_{m} = ( \dfrac{1}{2} + \dfrac{1}{\text{클러치 맞물림 개소 수}} ) \times \dfrac{60 {,} 000}{\text{매분 행정수}} = ( 0.5 + 0.125 ) \times \dfrac{60 {,} 000}{250} = 0.625 \times 240 = 150$ [ms]다. 안전거리는 $D = 1.6 T_{m} = 1.6 \times 150 = 240$ [mm]다.</t>
         </is>
       </c>
       <c r="AH48" s="32" t="inlineStr">
         <is>
-          <t>② 360 [mm] 는 계산과 맞지 않는다.&lt;br&gt;③ 400 [mm] 도 맞지 않는다.&lt;br&gt;④ 420 [mm] 도 맞지 않는다.</t>
+          <t>② 360 [mm]는 계산과 맞지 않는다.&lt;br&gt;③ 400 [mm] 도 맞지 않는다.&lt;br&gt;④ 420 [mm] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI48" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;양수기동식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;두 단계다 — $T_{m}$&lt;strong&gt; 을 먼저 구하고 1.6 을 곱한다&lt;/strong&gt;. $1 / 2$&lt;strong&gt; 은 「반 바퀴 돌 시간」, &lt;/strong&gt;$1 / n$&lt;strong&gt; 은 「맞물림 한 칸을 지날 시간」&lt;/strong&gt;이라는 뜻이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $D = 1.6 T_{m}$, $T_{m} = ( 1 / 2 + 1 / n ) \times 60 {,} 000 \div \mathrm{SPM}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;양수기동식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;두 단계다 — $T_{m}$&lt;strong&gt;을 먼저 구하고 1.6을 곱한다&lt;/strong&gt;. $1 / 2$&lt;strong&gt;은 「반 바퀴 돌 시간」, &lt;/strong&gt;$1 / n$&lt;strong&gt;은 「맞물림 한 칸을 지날 시간」&lt;/strong&gt;이라는 뜻이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $D = 1.6 T_{m}$, $T_{m} = ( 1 / 2 + 1 / n ) \times 60 {,} 000 \div \mathrm{SPM}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7518,17 +7522,17 @@
       </c>
       <c r="AG50" s="32" t="inlineStr">
         <is>
-          <t>표면속도 &lt;strong&gt;30 [m/min] 미만이면 원주의 1/3 이내&lt;/strong&gt;다. &lt;strong&gt;1/2.5 는 30 [m/min] 이상&lt;/strong&gt; 일 때다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;롤러기의 급정지거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;앞면 롤러의 표면속도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;급정지거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/min] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;앞면 롤러 원주의 1/3 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느릴수록 짧게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/min] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;앞면 롤러 원주의 1/2.5 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>표면속도 &lt;strong&gt;30 [m/min] 미만이면 원주의 1/3 이내&lt;/strong&gt;다. &lt;strong&gt;1/2.5는 30 [m/min] 이상&lt;/strong&gt;일 때다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;롤러기의 급정지거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;앞면 롤러의 표면속도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;급정지거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/min] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;앞면 롤러 원주의 1/3 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느릴수록 짧게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/min] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;앞면 롤러 원주의 1/2.5 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH50" s="32" t="inlineStr">
         <is>
-          <t>① 손 조작 급정지장치의 조작부를 전면과 후면에 각각 1개씩 수평으로 설치하는 것은 맞다.&lt;br&gt;③ 복부 조작 급정지장치를 밑면에서 0.8 ~ 1.1 [m] 에 설치하는 것도 맞다.&lt;br&gt;④ 조작부의 줄이 늘어지지 않고 충분한 인장강도를 가져야 하는 것도 맞다.</t>
+          <t>① 손 조작 급정지장치의 조작부를 전면과 후면에 각각 1개씩 수평으로 설치하는 것은 맞다.&lt;br&gt;③ 복부 조작 급정지장치를 밑면에서 0.8 ~ 1.1 [m]에 설치하는 것도 맞다.&lt;br&gt;④ 조작부의 줄이 늘어지지 않고 충분한 인장강도를 가져야 하는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI50" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방호장치 안전인증 고시 — 롤러기 급정지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;느린 기계일수록 더 짧게 세워야&lt;/strong&gt; 한다는 것이 뜻밖이지만, &lt;strong&gt;느릴수록 사람이 말려 들어갈 여지가 크기&lt;/strong&gt; 때문이다. &lt;strong&gt;1/3 과 1/2.5 를 바꿔 놓는 것&lt;/strong&gt;이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 [m/min] 미만이면 1/3&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방호장치 안전인증 고시 — 롤러기 급정지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;느린 기계일수록 더 짧게 세워야&lt;/strong&gt; 한다는 것이 뜻밖이지만, &lt;strong&gt;느릴수록 사람이 말려 들어갈 여지가 크기&lt;/strong&gt; 때문이다. &lt;strong&gt;1/3과 1/2.5를 바꿔 놓는 것&lt;/strong&gt;이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 [m/min] 미만이면 1/3&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7661,7 @@
       </c>
       <c r="AI51" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;초음파탐상검사(UT)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;안을 보려면 RT 나 UT&lt;/strong&gt; 뿐이다. &lt;strong&gt;RT 는 방사선 차폐와 자격이 필요해 현장에서 쓰기 어렵고, UT 는 장비만 있으면 된다&lt;/strong&gt;. &lt;strong&gt;「내부」라는 말이 나오면 UT&lt;/strong&gt;를 먼저 떠올린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내부 결함은 초음파탐상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;초음파탐상검사(UT)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;안을 보려면 RT 나 UT&lt;/strong&gt;뿐이다. &lt;strong&gt;RT는 방사선 차폐와 자격이 필요해 현장에서 쓰기 어렵고, UT는 장비만 있으면 된다&lt;/strong&gt;. &lt;strong&gt;「내부」라는 말이 나오면 UT&lt;/strong&gt;를 먼저 떠올린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내부 결함은 초음파탐상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8038,7 @@
       </c>
       <c r="AG54" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지름의 12배 이상&lt;/strong&gt; 일 때 쓴다.</t>
+          <t>&lt;strong&gt;지름의 12배 이상&lt;/strong&gt;일 때 쓴다.</t>
         </is>
       </c>
       <c r="AH54" s="32" t="inlineStr">
@@ -8683,12 +8687,12 @@
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;스트랜드(꼬임)의 수&lt;/strong&gt;다. &lt;strong&gt;6 × 19 는 스트랜드 6개, 각 스트랜드마다 소선 19가닥&lt;/strong&gt;이라는 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 표기 「6 × 19」&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;자리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앞의 6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;스트랜드(꼬임)의 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심강을 감싸는 다발의 수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뒤의 19&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 스트랜드 안의 소선 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가는 강선의 가닥 수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전체 소선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 × 19 = 114 가닥&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;스트랜드(꼬임)의 수&lt;/strong&gt;다. &lt;strong&gt;6 × 19는 스트랜드 6개, 각 스트랜드마다 소선 19가닥&lt;/strong&gt;이라는 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 표기 「6 × 19」&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;자리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앞의 6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;스트랜드(꼬임)의 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심강을 감싸는 다발의 수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뒤의 19&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 스트랜드 안의 소선 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가는 강선의 가닥 수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전체 소선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 × 19 = 114 가닥&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
-          <t>① 소선의 지름은 표기에 나타나지 않는다.&lt;br&gt;② 소선의 수량은 뒤의 19 다.&lt;br&gt;④ 로프의 인장강도도 표기에 나타나지 않는다.</t>
+          <t>① 소선의 지름은 표기에 나타나지 않는다.&lt;br&gt;② 소선의 수량은 뒤의 19다.&lt;br&gt;④ 로프의 인장강도도 표기에 나타나지 않는다.</t>
         </is>
       </c>
       <c r="AI59" s="32" t="inlineStr">
@@ -9070,17 +9074,17 @@
       </c>
       <c r="AG62" s="32" t="inlineStr">
         <is>
-          <t>$D = 1.6 T_{m}$ 이므로 $T_{m} = \dfrac{360}{1.6} = 225$ [ms] 다.</t>
+          <t>$D = 1.6 T_{m}$이므로 $T_{m} = \dfrac{360}{1.6} = 225$ [ms]다.</t>
         </is>
       </c>
       <c r="AH62" s="32" t="inlineStr">
         <is>
-          <t>① 90 [ms] 는 계산과 맞지 않는다.&lt;br&gt;② 125 [ms] 도 맞지 않는다.&lt;br&gt;④ 576 [ms] 는 1.6 을 곱해 버린 값이다.</t>
+          <t>① 90 [ms]는 계산과 맞지 않는다.&lt;br&gt;② 125 [ms] 도 맞지 않는다.&lt;br&gt;④ 576 [ms]는 1.6을 곱해 버린 값이다.</t>
         </is>
       </c>
       <c r="AI62" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;양수기동식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;46번의 거꾸로다. &lt;strong&gt;거리를 알고 시간을 구할 때는 1.6 으로 나눈다&lt;/strong&gt;. &lt;strong&gt;「맞물림 개소수 4개」는 이 물음에 쓰이지 않는 미끼&lt;/strong&gt;다 — $T_{m}$ 을 바로 묻고 있기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $T_{m} = D \div 1.6$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;양수기동식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;46번의 거꾸로다. &lt;strong&gt;거리를 알고 시간을 구할 때는 1.6으로 나눈다&lt;/strong&gt;. &lt;strong&gt;「맞물림 개소수 4개」는 이 물음에 쓰이지 않는 미끼&lt;/strong&gt;다 — $T_{m}$을 바로 묻고 있기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $T_{m} = D \div 1.6$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9337,7 @@
       </c>
       <c r="AH64" s="32" t="inlineStr">
         <is>
-          <t>① 2.5 [V] 이하는 제1종(몸의 대부분이 물에 젖은 상태)이다.&lt;br&gt;③ 50 [V] 이하는 제3종이다.&lt;br&gt;④ 75 [V] 라는 기준은 없다.</t>
+          <t>① 2.5 [V] 이하는 제1종(몸의 대부분이 물에 젖은 상태)이다.&lt;br&gt;③ 50 [V] 이하는 제3종이다.&lt;br&gt;④ 75 [V]라는 기준은 없다.</t>
         </is>
       </c>
       <c r="AI64" s="32" t="inlineStr">
@@ -9854,7 +9858,7 @@
       </c>
       <c r="AI68" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전작업 시의 잔류전하 방전&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「케이블」과 「콘덴서」라는 낱말이 나오면 잔류전하&lt;/strong&gt;를 떠올린다. &lt;strong&gt;전원을 끊고 나서도 만지면 감전&lt;/strong&gt; 되므로 &lt;strong&gt;반드시 방전한 뒤 검전&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;케이블과 콘덴서는 잔류전하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전작업 시의 잔류전하 방전&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「케이블」과 「콘덴서」라는 낱말이 나오면 잔류전하&lt;/strong&gt;를 떠올린다. &lt;strong&gt;전원을 끊고 나서도 만지면 감전&lt;/strong&gt;되므로 &lt;strong&gt;반드시 방전한 뒤 검전&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;케이블과 콘덴서는 잔류전하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10220,12 +10224,12 @@
       </c>
       <c r="AH71" s="32" t="inlineStr">
         <is>
-          <t>① 마그네슘은 약 80 [mJ] 다.&lt;br&gt;③ 알루미늄은 약 20 [mJ] 다.&lt;br&gt;④ 소맥분은 약 160 [mJ] 로 가장 크다.</t>
+          <t>① 마그네슘은 약 80 [mJ]다.&lt;br&gt;③ 알루미늄은 약 20 [mJ]다.&lt;br&gt;④ 소맥분은 약 160 [mJ]로 가장 크다.</t>
         </is>
       </c>
       <c r="AI71" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;분진의 최소발화에너지(MIE)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;값이 작을수록 작은 불꽃에도 터진다&lt;/strong&gt;. &lt;strong&gt;플라스틱 가루(폴리에틸렌)가 금속분보다 오히려 잘 붙는다&lt;/strong&gt;는 점이 뜻밖이다. &lt;strong&gt;정전기 방전 에너지가 이 값을 넘으면 폭발&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;폴리에틸렌이 가장 작다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;분진의 최소발화에너지(MIE)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;값이 작을수록 작은 불꽃에도 터진다&lt;/strong&gt;. &lt;strong&gt;플라스틱 가루(폴리에틸렌)가 금속분보다 오히려 잘 붙는다&lt;/strong&gt;는 점이 뜻밖이다. &lt;strong&gt;정전기 방전 에너지가 이 값을 넘으면 폭발&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;폴리에틸렌이 가장 작다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10572,7 @@
       </c>
       <c r="U74" s="32" t="inlineStr">
         <is>
-          <t>내측원통의 반경이 r 이고 외측원통의 반경이 R인 원통간극(r/R⁻¹(=0.368))에서 인가전압이 V인 경우 최대 전계 Er = V / (r ln(R/r)) 이다. 인가전압을 간극 간 공기의 절연파괴전압 전까지 낮은 전압에서 서서히 증가할 때의 설명으로 틀린 것은?</t>
+          <t>내측원통의 반경이 r이고 외측원통의 반경이 R인 원통간극(r/R⁻¹(=0.368))에서 인가전압이 V인 경우 최대 전계 Er = V / (r ln(R/r))이다. 인가전압을 간극 간 공기의 절연파괴전압 전까지 낮은 전압에서 서서히 증가할 때의 설명으로 틀린 것은?</t>
         </is>
       </c>
       <c r="V74" s="32" t="inlineStr"/>
@@ -10612,7 +10616,7 @@
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;원통 전극의 코로나 방전&lt;/strong&gt;&lt;br&gt;$E_{r} = V / ( r \ln ( R / r ) )$ 에서 $r$&lt;strong&gt; 가 커지면 &lt;/strong&gt;$E_{r}$&lt;strong&gt; 가 작아진다&lt;/strong&gt;. &lt;strong&gt;전하층이 내측 원통을 두툼하게 감싸 실질 반경을 키우는&lt;/strong&gt; 셈이라 전계가 낮아지고 방전이 안정된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;커지는 것은 내측 반경&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;원통 전극의 코로나 방전&lt;/strong&gt;&lt;br&gt;$E_{r} = V / ( r \ln ( R / r ) )$에서 $r$&lt;strong&gt;가 커지면 &lt;/strong&gt;$E_{r}$&lt;strong&gt;가 작아진다&lt;/strong&gt;. &lt;strong&gt;전하층이 내측 원통을 두툼하게 감싸 실질 반경을 키우는&lt;/strong&gt; 셈이라 전계가 낮아지고 방전이 안정된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;커지는 것은 내측 반경&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10731,17 +10735,17 @@
       </c>
       <c r="AG75" s="32" t="inlineStr">
         <is>
-          <t>최대공급전류는 $I = \dfrac{15 {,} 000}{100} = 150$ [A] 다. 허용 누설전류는 &lt;strong&gt;최대공급전류의 1/2,000&lt;/strong&gt;이므로 $150 / 2 {,} 000 = 0.075$ [A] 다.</t>
+          <t>최대공급전류는 $I = \dfrac{15 {,} 000}{100} = 150$ [A]다. 허용 누설전류는 &lt;strong&gt;최대공급전류의 1/2,000&lt;/strong&gt;이므로 $150 / 2 {,} 000 = 0.075$ [A]다.</t>
         </is>
       </c>
       <c r="AH75" s="32" t="inlineStr">
         <is>
-          <t>① 0.025 [A] 는 계산과 맞지 않는다.&lt;br&gt;② 0.045 [A] 도 맞지 않는다.&lt;br&gt;④ 0.085 [A] 도 맞지 않는다.</t>
+          <t>① 0.025 [A]는 계산과 맞지 않는다.&lt;br&gt;② 0.045 [A] 도 맞지 않는다.&lt;br&gt;④ 0.085 [A] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI75" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;누설전류의 허용값&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;저압측 전압 100 [V]&lt;/strong&gt;를 써야 한다 — &lt;strong&gt;6,600 [V] 는 1차측&lt;/strong&gt;이라 미끼다. &lt;strong&gt;1/2,000&lt;/strong&gt;이라는 비율을 외워 두면 두 줄로 끝난다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누설전류는 최대공급전류의 1/2,000&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;누설전류의 허용값&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;저압측 전압 100 [V]&lt;/strong&gt;를 써야 한다 — &lt;strong&gt;6,600 [V]는 1차측&lt;/strong&gt;이라 미끼다. &lt;strong&gt;1/2,000&lt;/strong&gt;이라는 비율을 외워 두면 두 줄로 끝난다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누설전류는 최대공급전류의 1/2,000&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10865,12 +10869,12 @@
       </c>
       <c r="AH76" s="32" t="inlineStr">
         <is>
-          <t>① 0.4 [MΩ] 은 400 [V] 이상의 값이다.&lt;br&gt;③ 0.2 [MΩ] 은 300 [V] 이하의 값이다.&lt;br&gt;④ 0.1 [MΩ] 은 150 [V] 이하의 값이다.</t>
+          <t>① 0.4 [MΩ]은 400 [V] 이상의 값이다.&lt;br&gt;③ 0.2 [MΩ]은 300 [V] 이하의 값이다.&lt;br&gt;④ 0.1 [MΩ]은 150 [V] 이하의 값이다.</t>
         </is>
       </c>
       <c r="AI76" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;저압전로의 절연저항 (옛 전기설비기술기준)&lt;/strong&gt;&lt;br&gt;네 값을 &lt;strong&gt;0.1 · 0.2 · 0.3 · 0.4&lt;/strong&gt;로 잡고, 경계를 &lt;strong&gt;150 · 300 · 400 [V]&lt;/strong&gt;로 짝지어 둔다. &lt;strong&gt;380 [V] 는 400 [V] 「미만」&lt;/strong&gt;이라 0.3 이다 — 한 칸 차이로 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0.1 · 0.2 · 0.3 · 0.4&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 절연저항 기준이 &lt;u&gt;세 줄로 단순해졌다&lt;/u&gt; — &lt;u&gt;SELV·PELV 는 0.5 [MΩ] 이상, FELV 와 500 [V] 이하는 1.0 [MΩ] 이상, 500 [V] 초과는 1.0 [MΩ] 이상&lt;/u&gt;. &lt;u&gt;현행 기준으로는 380 [V] 도 1.0 [MΩ] 이상&lt;/u&gt;이다. 옛 숫자(0.1 · 0.2 · 0.3 · 0.4)는 지금 쓰지 않는다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;저압전로의 절연저항 (옛 전기설비기술기준)&lt;/strong&gt;&lt;br&gt;네 값을 &lt;strong&gt;0.1 · 0.2 · 0.3 · 0.4&lt;/strong&gt;로 잡고, 경계를 &lt;strong&gt;150 · 300 · 400 [V]&lt;/strong&gt;로 짝지어 둔다. &lt;strong&gt;380 [V]는 400 [V] 「미만」&lt;/strong&gt;이라 0.3이다 — 한 칸 차이로 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0.1 · 0.2 · 0.3 · 0.4&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 절연저항 기준이 &lt;u&gt;세 줄로 단순해졌다&lt;/u&gt; — &lt;u&gt;SELV·PELV는 0.5 [MΩ] 이상, FELV와 500 [V] 이하는 1.0 [MΩ] 이상, 500 [V] 초과는 1.0 [MΩ] 이상&lt;/u&gt;. &lt;u&gt;현행 기준으로는 380 [V] 도 1.0 [MΩ] 이상&lt;/u&gt;이다. 옛 숫자(0.1 · 0.2 · 0.3 · 0.4)는 지금 쓰지 않는다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10994,7 +10998,7 @@
       </c>
       <c r="AH77" s="32" t="inlineStr">
         <is>
-          <t>② 고압용 1.5 [m] 는 기준보다 크다.&lt;br&gt;③ 1.5 [m] · 2.5 [m] 도 맞지 않는다.&lt;br&gt;④ 2.0 [m] · 2.5 [m] 도 맞지 않는다.</t>
+          <t>② 고압용 1.5 [m]는 기준보다 크다.&lt;br&gt;③ 1.5 [m] · 2.5 [m] 도 맞지 않는다.&lt;br&gt;④ 2.0 [m] · 2.5 [m] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI77" s="32" t="inlineStr">
@@ -11257,7 +11261,7 @@
       </c>
       <c r="AI79" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;내압방폭 금속관배선&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;방폭에는 언제나 두꺼운 후강전선관&lt;/strong&gt;이다. &lt;strong&gt;「박강」과 「후강」&lt;/strong&gt; 한 글자를 바꿔 놓는 것이 이 유형의 함정이다. &lt;strong&gt;5턱(약 8 [mm]) 이상&lt;/strong&gt;도 함께 잡는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;방폭에는 후강전선관&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;내압방폭 금속관배선&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;방폭에는 언제나 두꺼운 후강전선관&lt;/strong&gt;이다. &lt;strong&gt;「박강」과 「후강」&lt;/strong&gt;한 글자를 바꿔 놓는 것이 이 유형의 함정이다. &lt;strong&gt;5턱(약 8 [mm]) 이상&lt;/strong&gt;도 함께 잡는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;방폭에는 후강전선관&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11638,7 @@
       </c>
       <c r="AG82" s="32" t="inlineStr">
         <is>
-          <t>바닥은 &lt;strong&gt;고유저항이 작은(전기가 조금 통하는) 재료&lt;/strong&gt; 라야 한다. &lt;strong&gt;저항이 크면 전하가 발밑으로 빠져나가지 못한다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인체 대전의 예방대책&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대전방지제를 넣은 제전복 착용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옷에 쌓이지 않게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대전방지 성능이 있는 안전화 착용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;발을 통해 빠져나가게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바닥을 도전성 재료로 시공&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고유저항이 작아야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대전물체를 금속판으로 차폐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전계를 막는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업장의 습도를 60 ~ 70 [%] 로 유지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물기로 전하를 흘려보낸다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>바닥은 &lt;strong&gt;고유저항이 작은(전기가 조금 통하는) 재료&lt;/strong&gt;라야 한다. &lt;strong&gt;저항이 크면 전하가 발밑으로 빠져나가지 못한다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인체 대전의 예방대책&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대전방지제를 넣은 제전복 착용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옷에 쌓이지 않게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대전방지 성능이 있는 안전화 착용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;발을 통해 빠져나가게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바닥을 도전성 재료로 시공&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고유저항이 작아야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대전물체를 금속판으로 차폐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전계를 막는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업장의 습도를 60 ~ 70 [%]로 유지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물기로 전하를 흘려보낸다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH82" s="32" t="inlineStr">
@@ -11850,7 +11854,7 @@
       </c>
       <c r="U84" s="32" t="inlineStr">
         <is>
-          <t>비중이 1.5 이고, 직경이 74㎛인 분체가 종말속도 0.2m/s로 직경 6m의 사일로(silo)에서 질량유속 400kg/h로 흐를 때 평균 농도는 약 얼마인가?</t>
+          <t>비중이 1.5이고, 직경이 74㎛인 분체가 종말속도 0.2m/s로 직경 6m의 사일로(silo)에서 질량유속 400kg/h로 흐를 때 평균 농도는 약 얼마인가?</t>
         </is>
       </c>
       <c r="V84" s="32" t="inlineStr"/>
@@ -11884,17 +11888,17 @@
       </c>
       <c r="AG84" s="32" t="inlineStr">
         <is>
-          <t>단면적 $A = \pi \times 3^{2} \fallingdotseq 28.27$ [㎡] 이므로 부피유량은 $28.27 \times 0.2 = 5.655$ [㎥/s], 질량유량은 $400 / 3 {,} 600 \fallingdotseq 0.1111$ [kg/s] 다. 농도는 $\dfrac{0.1111}{5.655} \fallingdotseq 0.0197$ [kg/㎥] = &lt;strong&gt;19.8 [mg/L]&lt;/strong&gt;다.</t>
+          <t>단면적 $A = \pi \times 3^{2} \fallingdotseq 28.27$ [㎡]이므로 부피유량은 $28.27 \times 0.2 = 5.655$ [㎥/s], 질량유량은 $400 / 3 {,} 600 \fallingdotseq 0.1111$ [kg/s]다. 농도는 $\dfrac{0.1111}{5.655} \fallingdotseq 0.0197$ [kg/㎥] = &lt;strong&gt;19.8 [mg/L]&lt;/strong&gt;다.</t>
         </is>
       </c>
       <c r="AH84" s="32" t="inlineStr">
         <is>
-          <t>① 10.8 [mg/L] 는 계산과 맞지 않는다.&lt;br&gt;② 14.8 [mg/L] 도 맞지 않는다.&lt;br&gt;④ 25.8 [mg/L] 도 맞지 않는다.</t>
+          <t>① 10.8 [mg/L]는 계산과 맞지 않는다.&lt;br&gt;② 14.8 [mg/L] 도 맞지 않는다.&lt;br&gt;④ 25.8 [mg/L] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;분진의 평균 농도&lt;/strong&gt;&lt;br&gt;$\text{농도} = \dfrac{\text{질량유량}}{\text{부피유량}}$ 이다. &lt;strong&gt;1 [kg/㎥] = 1 [g/L] = 1,000 [mg/L]&lt;/strong&gt;라는 환산만 알면 마지막 단계가 쉽다. &lt;strong&gt;비중과 입자 지름은 종말속도를 정하는 값&lt;/strong&gt;이라 이 계산에는 쓰이지 않는 미끼다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;농도 = 질량유량 ÷ 부피유량&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;분진의 평균 농도&lt;/strong&gt;&lt;br&gt;$\text{농도} = \dfrac{\text{질량유량}}{\text{부피유량}}$이다. &lt;strong&gt;1 [kg/㎥] = 1 [g/L] = 1,000 [mg/L]&lt;/strong&gt;라는 환산만 알면 마지막 단계가 쉽다. &lt;strong&gt;비중과 입자 지름은 종말속도를 정하는 값&lt;/strong&gt;이라 이 계산에는 쓰이지 않는 미끼다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;농도 = 질량유량 ÷ 부피유량&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12013,7 +12017,7 @@
       </c>
       <c r="AG85" s="32" t="inlineStr">
         <is>
-          <t>$C_{2} H_{5} OH + 3 O_{2} \rightarrow 2 CO_{2} + 3 H_{2} O$ 다. &lt;strong&gt;탄소 2개는 CO₂ 2몰, 수소 6개는 H₂O 3몰&lt;/strong&gt;이 된다.</t>
+          <t>$C_{2} H_{5} OH + 3 O_{2} \rightarrow 2 CO_{2} + 3 H_{2} O$다. &lt;strong&gt;탄소 2개는 CO₂ 2몰, 수소 6개는 H₂O 3몰&lt;/strong&gt;이 된다.</t>
         </is>
       </c>
       <c r="AH85" s="32" t="inlineStr">
@@ -12529,17 +12533,17 @@
       </c>
       <c r="AG89" s="32" t="inlineStr">
         <is>
-          <t>$C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 ( n + m / 4 )}$ 이다. &lt;strong&gt;부탄은 &lt;/strong&gt;$n + m / 4 = 4 + 2.5 = 6.5$&lt;strong&gt; 로 가장 커서 &lt;/strong&gt;$C_{\mathrm{st}}$&lt;strong&gt; 가 가장 낮다&lt;/strong&gt;(약 3.1 [%]).&lt;div style="margin:12px 0 2px;font-weight:700"&gt;보기 물질의 완전조성농도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;$n + m / 4$&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;$C_{\mathrm{st}}$&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;메탄 CH₄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;9.5 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 높다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세틸렌 C₂H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7.7 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프로판 C₃H₈&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4.0 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부탄 C₄H₁₀&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.1 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 낮다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 ( n + m / 4 )}$이다. &lt;strong&gt;부탄은 &lt;/strong&gt;$n + m / 4 = 4 + 2.5 = 6.5$&lt;strong&gt;로 가장 커서 &lt;/strong&gt;$C_{\mathrm{st}}$&lt;strong&gt;가 가장 낮다&lt;/strong&gt;(약 3.1 [%]).&lt;div style="margin:12px 0 2px;font-weight:700"&gt;보기 물질의 완전조성농도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;$n + m / 4$&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;$C_{\mathrm{st}}$&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;메탄 CH₄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;9.5 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 높다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세틸렌 C₂H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7.7 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프로판 C₃H₈&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4.0 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부탄 C₄H₁₀&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.1 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 낮다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH89" s="32" t="inlineStr">
         <is>
-          <t>① 메탄은 9.5 [%] 로 가장 높다.&lt;br&gt;② 프로판은 4.0 [%] 다.&lt;br&gt;④ 아세틸렌은 약 7.7 [%] 다.</t>
+          <t>① 메탄은 9.5 [%]로 가장 높다.&lt;br&gt;② 프로판은 4.0 [%]다.&lt;br&gt;④ 아세틸렌은 약 7.7 [%]다.</t>
         </is>
       </c>
       <c r="AI89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;화학양론조성($C_{\mathrm{st}}$)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;탄소와 수소가 많을수록 산소가 더 많이 필요하므로 연료의 몫이 줄어든다&lt;/strong&gt; — 그래서 $C_{\mathrm{st}}$ 가 낮아진다. &lt;strong&gt;분자가 큰 것을 고르면 된다&lt;/strong&gt;는 어림으로도 풀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;분자가 클수록 &lt;/u&gt;$C_{\mathrm{st}}$&lt;u&gt; 가 낮다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;화학양론조성($C_{\mathrm{st}}$)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;탄소와 수소가 많을수록 산소가 더 많이 필요하므로 연료의 몫이 줄어든다&lt;/strong&gt; — 그래서 $C_{\mathrm{st}}$가 낮아진다. &lt;strong&gt;분자가 큰 것을 고르면 된다&lt;/strong&gt;는 어림으로도 풀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;분자가 클수록 &lt;/u&gt;$C_{\mathrm{st}}$&lt;u&gt;가 낮다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12668,7 +12672,7 @@
       </c>
       <c r="AI90" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최소발화에너지(MIE)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;온도 · 압력 · 산소 농도가 높을수록 최소발화에너지는 낮아진다&lt;/strong&gt; — 즉 &lt;strong&gt;더 쉽게 불붙는다&lt;/strong&gt;. &lt;strong&gt;공기(산소 21 [%])보다 순산소가 훨씬 위험&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산소 중에서 더 낮다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;최소발화에너지(MIE)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;온도 · 압력 · 산소 농도가 높을수록 최소발화에너지는 낮아진다&lt;/strong&gt; — 즉 &lt;strong&gt;더 쉽게 불붙는다&lt;/strong&gt;. &lt;strong&gt;공기(산소 21 [%])보다 순산소가 훨씬 위험&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산소 중에서 더 낮다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13045,12 +13049,12 @@
       </c>
       <c r="AG93" s="32" t="inlineStr">
         <is>
-          <t>$EI = \sum \dfrac{C_{i}}{\mathrm{TLV}_{i}} = \dfrac{20}{25} + \dfrac{20}{50} = 0.8 + 0.4 = 1.2$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;혼합물질의 노출지수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;내용&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$EI = C_{1} / \mathrm{TLV}_{1} + C_{2} / \mathrm{TLV}_{2} + \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상가작용을 가정&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;판정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;EI &amp;gt; 1 이면 노출기준 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항은 1.2 로 초과&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보정 노출기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{C_{1} + C_{2} + \cdots}{EI}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$EI = \sum \dfrac{C_{i}}{\mathrm{TLV}_{i}} = \dfrac{20}{25} + \dfrac{20}{50} = 0.8 + 0.4 = 1.2$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;혼합물질의 노출지수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;내용&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$EI = C_{1} / \mathrm{TLV}_{1} + C_{2} / \mathrm{TLV}_{2} + \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상가작용을 가정&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;판정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;EI &amp;gt; 1 이면 노출기준 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항은 1.2로 초과&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보정 노출기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{C_{1} + C_{2} + \cdots}{EI}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH93" s="32" t="inlineStr">
         <is>
-          <t>① 1.0 은 계산과 맞지 않는다.&lt;br&gt;③ 1.5 도 맞지 않는다.&lt;br&gt;④ 1.6 도 맞지 않는다.</t>
+          <t>① 1.0은 계산과 맞지 않는다.&lt;br&gt;③ 1.5 도 맞지 않는다.&lt;br&gt;④ 1.6 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI93" s="32" t="inlineStr">
@@ -13174,12 +13178,12 @@
       </c>
       <c r="AG94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;10 [%] 이하&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;하나의 MSDS 로 갈음할 수 있는 요건&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;요건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;혼합물로 된 제품의 구성성분이 같을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;각 구성성분의 함량변화가 10 [%] 이하일 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유사한 유해성을 가질 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;10 [%] 이하&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;하나의 MSDS로 갈음할 수 있는 요건&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;요건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;혼합물로 된 제품의 구성성분이 같을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;각 구성성분의 함량변화가 10 [%] 이하일 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유사한 유해성을 가질 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH94" s="32" t="inlineStr">
         <is>
-          <t>① 5 [%] 는 기준보다 엄격하다.&lt;br&gt;③ 15 [%] 는 기준보다 느슨하다.&lt;br&gt;④ 30 [%] 도 그렇다.</t>
+          <t>① 5 [%]는 기준보다 엄격하다.&lt;br&gt;③ 15 [%]는 기준보다 느슨하다.&lt;br&gt;④ 30 [%] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI94" s="32" t="inlineStr">
@@ -13694,7 +13698,7 @@
       </c>
       <c r="AG98" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방유장치&lt;/strong&gt;는 특수화학설비가 아니다. &lt;strong&gt;새어 나온 것을 담는 둑&lt;/strong&gt; 일 뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;특수화학설비 여섯 가지 (규칙 제273조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;설비&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발열반응이 일어나는 반응장치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가열시켜 부생가스가 발생하는 장치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;증류·정류·증발·추출 등 분리를 하는 장치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응폭주 등 이상 화학반응으로 위험물질이 발생할 우려가 있는 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;온도가 350 [℃] 이상이거나 게이지 압력이 980 [kPa] 이상인 상태에서 운전되는 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가열로 또는 가열기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;방유장치&lt;/strong&gt;는 특수화학설비가 아니다. &lt;strong&gt;새어 나온 것을 담는 둑&lt;/strong&gt;일 뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;특수화학설비 여섯 가지 (규칙 제273조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;설비&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발열반응이 일어나는 반응장치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가열시켜 부생가스가 발생하는 장치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;증류·정류·증발·추출 등 분리를 하는 장치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응폭주 등 이상 화학반응으로 위험물질이 발생할 우려가 있는 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;온도가 350 [℃] 이상이거나 게이지 압력이 980 [kPa] 이상인 상태에서 운전되는 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가열로 또는 가열기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH98" s="32" t="inlineStr">
@@ -14210,17 +14214,17 @@
       </c>
       <c r="AG102" s="32" t="inlineStr">
         <is>
-          <t>4 [%] 를 $x$, 10 [%] 를 $100 - x$ 라 하면 $0.04 x + 0.10 ( 100 - x ) = 0.06 \times 100$ 이다. $10 - 0.06 x = 6$ 에서 $x \fallingdotseq 66.67$ [kg] 이므로 10 [%] 는 33.33 [kg] 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가새표(십자법)로 푸는 법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;농도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;목표와의 차이&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 − 6 = 4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 − 4 = 2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 : 2 = 2 : 1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;66.67 : 33.33&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>4 [%]를 $x$, 10 [%]를 $100 - x$라 하면 $0.04 x + 0.10 ( 100 - x ) = 0.06 \times 100$이다. $10 - 0.06 x = 6$에서 $x \fallingdotseq 66.67$ [kg]이므로 10 [%]는 33.33 [kg]이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가새표(십자법)로 푸는 법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;농도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;목표와의 차이&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 − 6 = 4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 − 4 = 2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 : 2 = 2 : 1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;66.67 : 33.33&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH102" s="32" t="inlineStr">
         <is>
-          <t>① 50 : 50 이면 평균 농도가 7 [%] 가 된다.&lt;br&gt;② 56.2 : 43.8 도 계산과 맞지 않는다.&lt;br&gt;④ 80 : 20 이면 4.8 [%] 가 된다.</t>
+          <t>① 50 : 50 이면 평균 농도가 7 [%]가 된다.&lt;br&gt;② 56.2 : 43.8 도 계산과 맞지 않는다.&lt;br&gt;④ 80 : 20 이면 4.8 [%]가 된다.</t>
         </is>
       </c>
       <c r="AI102" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;용액의 혼합 계산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;목표 농도에서 먼 쪽을 적게, 가까운 쪽을 많이&lt;/strong&gt; 넣는다. &lt;strong&gt;6 [%] 는 4 [%] 에 더 가까우므로 4 [%] 용액이 더 많이&lt;/strong&gt; 들어간다 — 이 어림만으로도 ①②④가 걸러진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가까운 쪽을 많이&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;용액의 혼합 계산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;목표 농도에서 먼 쪽을 적게, 가까운 쪽을 많이&lt;/strong&gt; 넣는다. &lt;strong&gt;6 [%]는 4 [%]에 더 가까우므로 4 [%] 용액이 더 많이&lt;/strong&gt; 들어간다 — 이 어림만으로도 ①②④가 걸러진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가까운 쪽을 많이&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14344,7 +14348,7 @@
       </c>
       <c r="AH103" s="32" t="inlineStr">
         <is>
-          <t>① 5 [m] · 5 [m] 는 단관비계의 값이다.&lt;br&gt;② 6 [m] · 6 [m] 라는 짝은 없다.&lt;br&gt;④ 8 [m] · 6 [m] 는 수직과 수평이 뒤바뀐 값이다.</t>
+          <t>① 5 [m] · 5 [m]는 단관비계의 값이다.&lt;br&gt;② 6 [m] · 6 [m]라는 짝은 없다.&lt;br&gt;④ 8 [m] · 6 [m]는 수직과 수평이 뒤바뀐 값이다.</t>
         </is>
       </c>
       <c r="AI103" s="32" t="inlineStr">
@@ -14468,7 +14472,7 @@
       </c>
       <c r="AG104" s="32" t="inlineStr">
         <is>
-          <t>높이 8 [m] 이상인 비계다리에는 &lt;strong&gt;7 [m] 이내마다&lt;/strong&gt; 계단참을 둔다. 5 [m] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가설통로의 설치 기준 (규칙 제23조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;견고한 구조로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경사는 30° 이하로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경사가 15° 를 초과하면 미끄러지지 않는 구조로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;추락할 위험이 있는 장소에는 안전난간을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수직갱에 가설된 통로가 길이 15 [m] 이상이면 10 [m] 이내마다 계단참을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 8 [m] 이상인 비계다리에는 7 [m] 이내마다 계단참을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>높이 8 [m] 이상인 비계다리에는 &lt;strong&gt;7 [m] 이내마다&lt;/strong&gt; 계단참을 둔다. 5 [m]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가설통로의 설치 기준 (규칙 제23조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;견고한 구조로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경사는 30° 이하로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경사가 15° 를 초과하면 미끄러지지 않는 구조로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;추락할 위험이 있는 장소에는 안전난간을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수직갱에 가설된 통로가 길이 15 [m] 이상이면 10 [m] 이내마다 계단참을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 8 [m] 이상인 비계다리에는 7 [m] 이내마다 계단참을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH104" s="32" t="inlineStr">
@@ -14860,7 +14864,7 @@
       </c>
       <c r="AH107" s="32" t="inlineStr">
         <is>
-          <t>② 33.3 [t] 은 안전계수를 3 으로 놓았을 때의 값이다.&lt;br&gt;③ 40 [t] 은 2.5 로 놓았을 때다.&lt;br&gt;④ 50 [t] 은 2 로 놓았을 때다.</t>
+          <t>② 33.3 [t]은 안전계수를 3으로 놓았을 때의 값이다.&lt;br&gt;③ 40 [t]은 2.5로 놓았을 때다.&lt;br&gt;④ 50 [t]은 2로 놓았을 때다.</t>
         </is>
       </c>
       <c r="AI107" s="32" t="inlineStr">
@@ -14984,7 +14988,7 @@
       </c>
       <c r="AG108" s="32" t="inlineStr">
         <is>
-          <t>교량은 &lt;strong&gt;최대 지간길이 50 [m] 이상&lt;/strong&gt; 이라야 대상이다. 40 [m] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건설공사 계획서 제출 대상 (영 제42조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상 공사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지상높이 31 [m] 이상인 건축물 또는 인공구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;31 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 3만 [㎡] 이상인 건축물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3만 [㎡]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 5천 [㎡] 이상인 문화·집회시설, 판매·운수시설, 종합병원, 관광숙박시설, 지하도상가, 냉동·냉장 창고시설&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5천 [㎡]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 지간길이 50 [m] 이상인 교량 건설공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [m] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널 건설공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;크기와 무관&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다목적댐·발전용댐, 저수용량 2천만 [t] 이상의 용수 전용댐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;깊이 10 [m] 이상인 굴착공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>교량은 &lt;strong&gt;최대 지간길이 50 [m] 이상&lt;/strong&gt;이라야 대상이다. 40 [m]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건설공사 계획서 제출 대상 (영 제42조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상 공사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지상높이 31 [m] 이상인 건축물 또는 인공구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;31 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 3만 [㎡] 이상인 건축물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3만 [㎡]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 5천 [㎡] 이상인 문화·집회시설, 판매·운수시설, 종합병원, 관광숙박시설, 지하도상가, 냉동·냉장 창고시설&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5천 [㎡]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 지간길이 50 [m] 이상인 교량 건설공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [m]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널 건설공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;크기와 무관&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다목적댐·발전용댐, 저수용량 2천만 [t] 이상의 용수 전용댐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;깊이 10 [m] 이상인 굴착공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH108" s="32" t="inlineStr">
@@ -15252,7 +15256,7 @@
       </c>
       <c r="AI110" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;소일네일링(soil nailing) 공법&lt;/strong&gt;&lt;br&gt;소일네일링은 &lt;strong&gt;지반에 구멍을 뚫고 강봉을 넣어 그라우팅으로 굳혀 흙과 한 몸으로 만드는&lt;/strong&gt; 공법이다. &lt;strong&gt;구멍이 스스로 서 있고 그라우팅이 붙을 만한 흙&lt;/strong&gt; 이라야 하는데, &lt;strong&gt;점성이 있는 모래와 자갈은 그 조건에 맞는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;점성 있는 모래·자갈은 오히려 알맞다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;소일네일링(soil nailing) 공법&lt;/strong&gt;&lt;br&gt;소일네일링은 &lt;strong&gt;지반에 구멍을 뚫고 강봉을 넣어 그라우팅으로 굳혀 흙과 한 몸으로 만드는&lt;/strong&gt; 공법이다. &lt;strong&gt;구멍이 스스로 서 있고 그라우팅이 붙을 만한 흙&lt;/strong&gt;이라야 하는데, &lt;strong&gt;점성이 있는 모래와 자갈은 그 조건에 맞는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;점성 있는 모래·자갈은 오히려 알맞다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15371,17 +15375,17 @@
       </c>
       <c r="AG111" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;N 값 50 이상이면 대단히 조밀&lt;/strong&gt; 하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;N 값과 모래의 상대밀도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;N 값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상대밀도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0 ~ 4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;몹시 느슨하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4 ~ 10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느슨하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10 ~ 30&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보통이다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 ~ 50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조밀하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대단히 조밀하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;N 값 50 이상이면 대단히 조밀&lt;/strong&gt;하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;N 값과 모래의 상대밀도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;N 값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상대밀도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0 ~ 4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;몹시 느슨하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4 ~ 10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느슨하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10 ~ 30&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보통이다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 ~ 50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조밀하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대단히 조밀하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH111" s="32" t="inlineStr">
         <is>
-          <t>① 몹시 느슨한 것은 N 값 0 ~ 4 다.&lt;br&gt;② 느슨한 것은 4 ~ 10 이다.&lt;br&gt;③ 보통은 10 ~ 30 이다.</t>
+          <t>① 몹시 느슨한 것은 N 값 0 ~ 4다.&lt;br&gt;② 느슨한 것은 4 ~ 10이다.&lt;br&gt;③ 보통은 10 ~ 30이다.</t>
         </is>
       </c>
       <c r="AI111" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;표준관입시험(SPT)의 N 값&lt;/strong&gt;&lt;br&gt;다섯 구간을 &lt;strong&gt;4 · 10 · 30 · 50&lt;/strong&gt;으로 나눈다. &lt;strong&gt;N 값이 클수록 단단하다&lt;/strong&gt; — &lt;strong&gt;여러 번 쳐야 겨우 들어간다&lt;/strong&gt;는 뜻이다. &lt;strong&gt;63.5 [kg] 추를 76 [cm] 에서 떨어뜨려 30 [cm] 관입&lt;/strong&gt; 시킨다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;50 이상이면 대단히 조밀&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;표준관입시험(SPT)의 N 값&lt;/strong&gt;&lt;br&gt;다섯 구간을 &lt;strong&gt;4 · 10 · 30 · 50&lt;/strong&gt;으로 나눈다. &lt;strong&gt;N 값이 클수록 단단하다&lt;/strong&gt; — &lt;strong&gt;여러 번 쳐야 겨우 들어간다&lt;/strong&gt;는 뜻이다. &lt;strong&gt;63.5 [kg] 추를 76 [cm]에서 떨어뜨려 30 [cm] 관입&lt;/strong&gt; 시킨다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;50 이상이면 대단히 조밀&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15767,7 +15771,7 @@
       </c>
       <c r="AH114" s="32" t="inlineStr">
         <is>
-          <t>② A 가 8 이면 기준보다 촘촘하다.&lt;br&gt;③ A 가 10, B 가 3 이면 내민 길이가 기준보다 길다.&lt;br&gt;④ A 가 8, B 가 3 이면 둘 다 어긋난다.</t>
+          <t>② A가 8 이면 기준보다 촘촘하다.&lt;br&gt;③ A가 10, B가 3 이면 내민 길이가 기준보다 길다.&lt;br&gt;④ A가 8, B가 3 이면 둘 다 어긋난다.</t>
         </is>
       </c>
       <c r="AI114" s="32" t="inlineStr">
@@ -16030,7 +16034,7 @@
       </c>
       <c r="AI116" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;개착식 터널공법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「파고 → 짓고 → 덮는다」&lt;/strong&gt;는 설명이 곧 cut and cover 다. &lt;strong&gt;얕은 곳에는 개착식이 싸고 빠르지만 지상 교통을 막는다&lt;/strong&gt;는 단점이 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;파고 짓고 덮으면 개착식&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;개착식 터널공법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「파고 → 짓고 → 덮는다」&lt;/strong&gt;는 설명이 곧 cut and cover다. &lt;strong&gt;얕은 곳에는 개착식이 싸고 빠르지만 지상 교통을 막는다&lt;/strong&gt;는 단점이 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;파고 짓고 덮으면 개착식&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16149,7 +16153,7 @@
       </c>
       <c r="AG117" s="32" t="inlineStr">
         <is>
-          <t>굴착공사는 &lt;strong&gt;깊이 10 [m] 이상&lt;/strong&gt; 이라야 대상이다. 5 [m] 가 아니다.</t>
+          <t>굴착공사는 &lt;strong&gt;깊이 10 [m] 이상&lt;/strong&gt;이라야 대상이다. 5 [m]가 아니다.</t>
         </is>
       </c>
       <c r="AH117" s="32" t="inlineStr">
@@ -16288,7 +16292,7 @@
       </c>
       <c r="AI118" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산업안전보건법 시행령 제74조 — 안전인증 대상 기계 등&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;설치·이전 시 대상은 「크 · 리 · 곤」 셋뿐&lt;/strong&gt;이다. &lt;strong&gt;셋 모두 현장에서 조립해 세우는 양중기&lt;/strong&gt; 라서 &lt;strong&gt;세우는 방식 자체가 위험&lt;/strong&gt; 하기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;설치·이전은 크 · 리 · 곤 셋&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행령 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EB%A0%B9/%EC%A0%9C74%EC%A1%B0" target="_blank"&gt;제74조(안전인증대상기계등)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건법 시행령 · 시행 2026. 8. 1.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 법 제84조제1항에서 "대통령령으로 정하는 것"이란 다음 각 호의 어느 하나에 해당하는 것을 말한다.&lt;br&gt; 1. 다음 각 목의 어느 하나에 해당하는 기계 또는 설비&lt;br&gt; 가. 프레스&lt;br&gt; 나. 전단기 및 절곡기(折曲機)&lt;br&gt; 다. 크레인&lt;br&gt; 라. 리프트&lt;br&gt; 마. 압력용기&lt;br&gt; 바. 롤러기&lt;br&gt; 사. 사출성형기(射出成形機)&lt;br&gt; 아. 고소(高所) 작업대&lt;br&gt; 자. 곤돌라&lt;br&gt; 2. 다음 각 목의 어느 하나에 해당하는 방호장치&lt;br&gt; 가. 프레스 및 전단기 방호장치&lt;br&gt; 나. 양중기용(揚重機用) 과부하 방지장치&lt;br&gt; 다. 보일러 압력방출용 안전밸브&lt;br&gt; 라. 압력용기 압력방출용 안전밸브&lt;br&gt; 마. 압력용기 압력방출용 파열판&lt;br&gt; 바. 절연용 방호구 및 활선작업용(活線作業用) 기구&lt;br&gt; 사. 방폭구조(防爆構造) 전기기계ㆍ기구 및 부품&lt;br&gt; 아. 추락ㆍ낙하 및 붕괴 등의 위험 방지 및 보호에 필요한 가설기자재로서 고용노동부장관이 정하여 고시하는 것&lt;br&gt; 자. 충돌ㆍ협착 등의 위험 방지에 필요한 산업용 로봇 방호장치로서 고용노동부장관이 정하여 고시하는 것&lt;br&gt; 3. 다음 각 목의 어느 하나에 해당하는 보호구&lt;br&gt; 가. 추락 및 감전 위험방지용 안전모&lt;br&gt; 나. 안전화&lt;br&gt; 다. 안전장갑&lt;br&gt; 라. 방진마스크&lt;br&gt; 마. 방독마스크&lt;br&gt; 바. 송기(送氣)마스크&lt;br&gt; 사. 전동식 호흡보호구&lt;br&gt; 아. 보호복&lt;br&gt; 자. 안전대&lt;br&gt; 차. 차광(遮光) 및 비산물(飛散物) 위험방지용 보안경&lt;br&gt; 카. 용접용 보안면&lt;br&gt; 타. 방음용 귀마개 또는 귀덮개&lt;br&gt;② 안전인증대상기계등의 세부적인 종류, 규격 및 형식은 고용노동부장관이 정하여 고시한다.&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;산업안전보건법 시행령 제74조 — 안전인증 대상 기계 등&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;설치·이전 시 대상은 「크 · 리 · 곤」 셋뿐&lt;/strong&gt;이다. &lt;strong&gt;셋 모두 현장에서 조립해 세우는 양중기&lt;/strong&gt; 라서 &lt;strong&gt;세우는 방식 자체가 위험&lt;/strong&gt;하기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;설치·이전은 크 · 리 · 곤 셋&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행령 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EB%A0%B9/%EC%A0%9C74%EC%A1%B0" target="_blank"&gt;제74조(안전인증대상기계등)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건법 시행령 · 시행 2026. 8. 1.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 법 제84조제1항에서 "대통령령으로 정하는 것"이란 다음 각 호의 어느 하나에 해당하는 것을 말한다.&lt;br&gt; 1. 다음 각 목의 어느 하나에 해당하는 기계 또는 설비&lt;br&gt; 가. 프레스&lt;br&gt; 나. 전단기 및 절곡기(折曲機)&lt;br&gt; 다. 크레인&lt;br&gt; 라. 리프트&lt;br&gt; 마. 압력용기&lt;br&gt; 바. 롤러기&lt;br&gt; 사. 사출성형기(射出成形機)&lt;br&gt; 아. 고소(高所) 작업대&lt;br&gt; 자. 곤돌라&lt;br&gt; 2. 다음 각 목의 어느 하나에 해당하는 방호장치&lt;br&gt; 가. 프레스 및 전단기 방호장치&lt;br&gt; 나. 양중기용(揚重機用) 과부하 방지장치&lt;br&gt; 다. 보일러 압력방출용 안전밸브&lt;br&gt; 라. 압력용기 압력방출용 안전밸브&lt;br&gt; 마. 압력용기 압력방출용 파열판&lt;br&gt; 바. 절연용 방호구 및 활선작업용(活線作業用) 기구&lt;br&gt; 사. 방폭구조(防爆構造) 전기기계ㆍ기구 및 부품&lt;br&gt; 아. 추락ㆍ낙하 및 붕괴 등의 위험 방지 및 보호에 필요한 가설기자재로서 고용노동부장관이 정하여 고시하는 것&lt;br&gt; 자. 충돌ㆍ협착 등의 위험 방지에 필요한 산업용 로봇 방호장치로서 고용노동부장관이 정하여 고시하는 것&lt;br&gt; 3. 다음 각 목의 어느 하나에 해당하는 보호구&lt;br&gt; 가. 추락 및 감전 위험방지용 안전모&lt;br&gt; 나. 안전화&lt;br&gt; 다. 안전장갑&lt;br&gt; 라. 방진마스크&lt;br&gt; 마. 방독마스크&lt;br&gt; 바. 송기(送氣)마스크&lt;br&gt; 사. 전동식 호흡보호구&lt;br&gt; 아. 보호복&lt;br&gt; 자. 안전대&lt;br&gt; 차. 차광(遮光) 및 비산물(飛散物) 위험방지용 보안경&lt;br&gt; 카. 용접용 보안면&lt;br&gt; 타. 방음용 귀마개 또는 귀덮개&lt;br&gt;② 안전인증대상기계등의 세부적인 종류, 규격 및 형식은 고용노동부장관이 정하여 고시한다.&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -16675,7 +16679,7 @@
       </c>
       <c r="AI121" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;콘크리트 강도의 영향 요소&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;콘크리트 강도를 가장 크게 좌우하는 것은 물–시멘트비&lt;/strong&gt;다. &lt;strong&gt;물이 많으면 반죽은 묽어 다루기 쉽지만 굳은 뒤 빈틈이 많아 약해진다&lt;/strong&gt;. &lt;strong&gt;거푸집은 모양을 잡는 틀&lt;/strong&gt; 일 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;거푸집 모양은 강도와 무관&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;콘크리트 강도의 영향 요소&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;콘크리트 강도를 가장 크게 좌우하는 것은 물–시멘트비&lt;/strong&gt;다. &lt;strong&gt;물이 많으면 반죽은 묽어 다루기 쉽지만 굳은 뒤 빈틈이 많아 약해진다&lt;/strong&gt;. &lt;strong&gt;거푸집은 모양을 잡는 틀&lt;/strong&gt;일 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;거푸집 모양은 강도와 무관&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16794,7 +16798,7 @@
       </c>
       <c r="AG122" s="32" t="inlineStr">
         <is>
-          <t>지름의 감소는 &lt;strong&gt;공칭지름의 7 [%] 를 초과&lt;/strong&gt; 할 때 사용 금지다. 5 [%] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용 금지 기준 (규칙 제63조·제166조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용 금지 사유&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수가 10 [%] 이상인 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소가 공칭지름의 7 [%] 를 초과하는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [%] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열과 전기충격에 의해 손상된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>지름의 감소는 &lt;strong&gt;공칭지름의 7 [%]를 초과&lt;/strong&gt;할 때 사용 금지다. 5 [%]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용 금지 기준 (규칙 제63조·제166조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용 금지 사유&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수가 10 [%] 이상인 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소가 공칭지름의 7 [%]를 초과하는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [%]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열과 전기충격에 의해 손상된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH122" s="32" t="inlineStr">
@@ -16804,7 +16808,7 @@
       </c>
       <c r="AI122" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제63조 — 달비계의 와이어로프&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;소선 10 [%], 지름 7 [%]&lt;/strong&gt; 두 숫자를 짝으로 잡는다. &lt;strong&gt;끊어진 줄은 10, 가늘어진 정도는 7&lt;/strong&gt;이다. &lt;strong&gt;5 나 8 로 비틀어 놓는 것&lt;/strong&gt;이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;소선 10 [%], 지름 7 [%]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C63%EC%A1%B0" target="_blank"&gt;제63조(달비계의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 곤돌라형 달비계를 설치하는 경우에는 다음 각 호의 사항을 준수해야 한다. &amp;lt;개정 2021.11.19&amp;gt;&lt;br&gt; 1. 다음 각 목의 어느 하나에 해당하는 와이어로프를 달비계에 사용해서는 아니 된다.&lt;br&gt; 가. 이음매가 있는 것&lt;br&gt; 나. 와이어로프의 한 꼬임[(스트랜드(strand)를 말한다. 이하 같다)]에서 끊어진 소선(素線)[필러(pillar)선은 제외한다)]의 수가 10퍼센트 이상(비자전로프의 경우에는 끊어진 소선의 수가 와이어로프 호칭지름의 6배 길이 이내에서 4개 이상이거나 호칭지름 30배 길이 이내에서 8개 이상)인 것&lt;br&gt;▶  다. &lt;strong&gt;지름의 감소가 공칭지름의 7&lt;/strong&gt;퍼센트를 초과하는 것&lt;br&gt; 라. 꼬인 것&lt;br&gt; 마. 심하게 변형되거나 부식된 것&lt;br&gt; 바. 열과 전기충격에 의해 손상된 것&lt;br&gt; 2. 다음 각 목의 어느 하나에 해당하는 달기 체인을 달비계에 사용해서는 아니 된다.&lt;br&gt; 가. 달기 체인의 길이가 달기 체인이 제조된 때의 길이의 5퍼센트를 초과한 것&lt;br&gt; 나. 링의 단면지름이 달기 체인이 제조된 때의 해당 링의 지름의 10퍼센트를 초과하여 감소한 것&lt;br&gt; 다. 균열이 있거나 심하게 변형된 것&lt;br&gt; 3. 삭제&amp;lt;2021.11.19&amp;gt;&lt;br&gt; 4. 달기 강선 및 달기 강대는 심하게 손상ㆍ변형 또는 부식된 것을 사용하지 않도록 할 것&lt;br&gt; 5. 달기 와이어로프, 달기 체인, 달기 강선, 달기 강대는 한쪽 끝을 비계의 보 등에, 다른 쪽 끝을 내민 보, 앵커볼트 또는 건축물의 보 등에 각각 풀리지 않도록 설치할 것&lt;br&gt; 6. 작업발판은 폭을 40센티미터 이상으로 하고 틈새가 없도록 할 것&lt;br&gt; 7. 작업발판의 재료는 뒤집히거나 떨어지지 않도록 비계의 보 등에 연결하거나 고정시킬 것&lt;br&gt; 8. 비계가 흔들리거나 뒤집히는 것을 방지하기 위하여 비계의 보ㆍ작업발판 등에 버팀을 설치하는 등 필요한 조치를 할 것&lt;br&gt; 9. 선반 비계에서는 보의 접속부 및 교차부를 철선ㆍ이음철물 등을 사용하여 확실하게 접속시키거나 단단하게 연결시킬 것&lt;br&gt; 10. 근로자의 추락 위험을 방지하기 위하여 다음 각 목의 조치를 할 것&lt;br&gt; 가. 달비계에 구명줄을 설치할 것&lt;br&gt; 나. 근로자에게 안전대를 착용하도록 하고 근로자가 착용한 안전줄을 달비계의 구명줄에 체결(締結)하도록 할 것&lt;br&gt; 다. 달비계에 안전난간을 설치할 수 있는 구조인 경우에는 달비계에 안전난간을 설치할 것&lt;br&gt;② 사업주는 작업의자형 달비계를 설치하는 경우에는 다음 각 호의 사항을 준수해야 한다. &amp;lt;신설 2021.11.19&amp;gt;&lt;br&gt; 1. 달비계의 작업대는 나무 등 근로자의 하중을 견딜 수 있는 강도의 재료를 사용하여 견고한 구조로 제작할 것&lt;br&gt; 2. 작업대의 4개 모서리에 로프를 매달아 작업대가 뒤집히거나 떨어지지 않도록 연결할 것&lt;br&gt; 3. 작업용 섬유로프는 콘크리트에 매립된 고리, 건축물의 콘크리트 또는 철재 구조물 등 2개 이상의 견고한 고정점에 풀리지 않도록 결속(結束)할 것&lt;br&gt; 4. 작업용 섬유로프와 구명줄은 다른 고정점에 결속되도록 할 것&lt;br&gt; 5. 작업하는 근로자의 하중을 견딜 수 있을 정도의 강도를 가진 작업용 섬유로프, 구명줄 및 고정점을 사용할 것&lt;br&gt; 6. 근로자가 작업용 섬유로프에 작업대를 연결하여 하강하는 방법으로 작업을 하는 경우 근로자의 조종 없이는 작업대가 하강하지 않도록 할 것&lt;br&gt; 7. 작업용 섬유로프 또는 구명줄이 결속된 고정점의 로프는 다른 사람이 풀지 못하게 하고 작업 중임을 알리는 경고표지를 부착할 것&lt;br&gt; 8. 작업용 섬유로프와 구명줄이 건물이나 구조물의 끝부분, 날카로운 물체 등에 의하여 절단되거나 마모(磨耗)될 우려가 있는 경우에는 로프에 이를 방지할 수 있는 보호 덮개를 씌우는 등의 조치를 할 것&lt;br&gt; 9. 달비계에 다음 각 목의 작업용 섬유로프 또는 안전대의 섬유벨트를 사용하지 않을 것&lt;br&gt; 가. 꼬임이 끊어진 것&lt;br&gt; 나. 심하게 손상되거나 부식된 것&lt;br&gt; 다. 2개 이상의 작업용 섬유로프 또는 섬유벨트를 연결한 것&lt;br&gt; 라. 작업높이보다 길이가 짧은 것&lt;br&gt; 10. 근로자의 추락 위험을 방지하기 위하여 다음 각 목의 조치를 할 것&lt;br&gt; 가. 달비계에 구명줄을 설치할 것&lt;br&gt; 나. 근로자에게 안전대를 착용하도록 하고 근로자가 착용한 안전줄을 달비계의 구명줄에 체결(締結)하도록 할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제63조 — 달비계의 와이어로프&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;소선 10 [%], 지름 7 [%]&lt;/strong&gt; 두 숫자를 짝으로 잡는다. &lt;strong&gt;끊어진 줄은 10, 가늘어진 정도는 7&lt;/strong&gt;이다. &lt;strong&gt;5 나 8로 비틀어 놓는 것&lt;/strong&gt;이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;소선 10 [%], 지름 7 [%]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C63%EC%A1%B0" target="_blank"&gt;제63조(달비계의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 곤돌라형 달비계를 설치하는 경우에는 다음 각 호의 사항을 준수해야 한다. &amp;lt;개정 2021.11.19&amp;gt;&lt;br&gt; 1. 다음 각 목의 어느 하나에 해당하는 와이어로프를 달비계에 사용해서는 아니 된다.&lt;br&gt; 가. 이음매가 있는 것&lt;br&gt; 나. 와이어로프의 한 꼬임[(스트랜드(strand)를 말한다. 이하 같다)]에서 끊어진 소선(素線)[필러(pillar)선은 제외한다)]의 수가 10퍼센트 이상(비자전로프의 경우에는 끊어진 소선의 수가 와이어로프 호칭지름의 6배 길이 이내에서 4개 이상이거나 호칭지름 30배 길이 이내에서 8개 이상)인 것&lt;br&gt;▶  다. &lt;strong&gt;지름의 감소가 공칭지름의 7&lt;/strong&gt;퍼센트를 초과하는 것&lt;br&gt; 라. 꼬인 것&lt;br&gt; 마. 심하게 변형되거나 부식된 것&lt;br&gt; 바. 열과 전기충격에 의해 손상된 것&lt;br&gt; 2. 다음 각 목의 어느 하나에 해당하는 달기 체인을 달비계에 사용해서는 아니 된다.&lt;br&gt; 가. 달기 체인의 길이가 달기 체인이 제조된 때의 길이의 5퍼센트를 초과한 것&lt;br&gt; 나. 링의 단면지름이 달기 체인이 제조된 때의 해당 링의 지름의 10퍼센트를 초과하여 감소한 것&lt;br&gt; 다. 균열이 있거나 심하게 변형된 것&lt;br&gt; 3. 삭제&amp;lt;2021.11.19&amp;gt;&lt;br&gt; 4. 달기 강선 및 달기 강대는 심하게 손상ㆍ변형 또는 부식된 것을 사용하지 않도록 할 것&lt;br&gt; 5. 달기 와이어로프, 달기 체인, 달기 강선, 달기 강대는 한쪽 끝을 비계의 보 등에, 다른 쪽 끝을 내민 보, 앵커볼트 또는 건축물의 보 등에 각각 풀리지 않도록 설치할 것&lt;br&gt; 6. 작업발판은 폭을 40센티미터 이상으로 하고 틈새가 없도록 할 것&lt;br&gt; 7. 작업발판의 재료는 뒤집히거나 떨어지지 않도록 비계의 보 등에 연결하거나 고정시킬 것&lt;br&gt; 8. 비계가 흔들리거나 뒤집히는 것을 방지하기 위하여 비계의 보ㆍ작업발판 등에 버팀을 설치하는 등 필요한 조치를 할 것&lt;br&gt; 9. 선반 비계에서는 보의 접속부 및 교차부를 철선ㆍ이음철물 등을 사용하여 확실하게 접속시키거나 단단하게 연결시킬 것&lt;br&gt; 10. 근로자의 추락 위험을 방지하기 위하여 다음 각 목의 조치를 할 것&lt;br&gt; 가. 달비계에 구명줄을 설치할 것&lt;br&gt; 나. 근로자에게 안전대를 착용하도록 하고 근로자가 착용한 안전줄을 달비계의 구명줄에 체결(締結)하도록 할 것&lt;br&gt; 다. 달비계에 안전난간을 설치할 수 있는 구조인 경우에는 달비계에 안전난간을 설치할 것&lt;br&gt;② 사업주는 작업의자형 달비계를 설치하는 경우에는 다음 각 호의 사항을 준수해야 한다. &amp;lt;신설 2021.11.19&amp;gt;&lt;br&gt; 1. 달비계의 작업대는 나무 등 근로자의 하중을 견딜 수 있는 강도의 재료를 사용하여 견고한 구조로 제작할 것&lt;br&gt; 2. 작업대의 4개 모서리에 로프를 매달아 작업대가 뒤집히거나 떨어지지 않도록 연결할 것&lt;br&gt; 3. 작업용 섬유로프는 콘크리트에 매립된 고리, 건축물의 콘크리트 또는 철재 구조물 등 2개 이상의 견고한 고정점에 풀리지 않도록 결속(結束)할 것&lt;br&gt; 4. 작업용 섬유로프와 구명줄은 다른 고정점에 결속되도록 할 것&lt;br&gt; 5. 작업하는 근로자의 하중을 견딜 수 있을 정도의 강도를 가진 작업용 섬유로프, 구명줄 및 고정점을 사용할 것&lt;br&gt; 6. 근로자가 작업용 섬유로프에 작업대를 연결하여 하강하는 방법으로 작업을 하는 경우 근로자의 조종 없이는 작업대가 하강하지 않도록 할 것&lt;br&gt; 7. 작업용 섬유로프 또는 구명줄이 결속된 고정점의 로프는 다른 사람이 풀지 못하게 하고 작업 중임을 알리는 경고표지를 부착할 것&lt;br&gt; 8. 작업용 섬유로프와 구명줄이 건물이나 구조물의 끝부분, 날카로운 물체 등에 의하여 절단되거나 마모(磨耗)될 우려가 있는 경우에는 로프에 이를 방지할 수 있는 보호 덮개를 씌우는 등의 조치를 할 것&lt;br&gt; 9. 달비계에 다음 각 목의 작업용 섬유로프 또는 안전대의 섬유벨트를 사용하지 않을 것&lt;br&gt; 가. 꼬임이 끊어진 것&lt;br&gt; 나. 심하게 손상되거나 부식된 것&lt;br&gt; 다. 2개 이상의 작업용 섬유로프 또는 섬유벨트를 연결한 것&lt;br&gt; 라. 작업높이보다 길이가 짧은 것&lt;br&gt; 10. 근로자의 추락 위험을 방지하기 위하여 다음 각 목의 조치를 할 것&lt;br&gt; 가. 달비계에 구명줄을 설치할 것&lt;br&gt; 나. 근로자에게 안전대를 착용하도록 하고 근로자가 착용한 안전줄을 달비계의 구명줄에 체결(締結)하도록 할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
